--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_v8【迷宫-能力词条】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_v8【迷宫-能力词条】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E6A48D-E851-4306-9AAD-9EFE82EED619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A7E337-076B-4970-BBB8-23FCBC5D7E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="768">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2720,11 +2720,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3050301:10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每攻击8次释放1次冰霜新星，造成冰元素伤害</t>
+    <t>3050301:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102,3041201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+%s，暴击伤害+%s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+%s，暴击率+%s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102,3041301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:4000_3041201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:5500_3041201:500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:10000_3041201:500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:6500_3041201:500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:7500_3041201:500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:8500_3041201:500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:5000_3041301:2500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3041501:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:5000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2732,67 +2780,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3050301:5000_3550100:1_3551000:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:7500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102,3041201</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击+%s，暴击伤害+%s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击+%s，暴击率+%s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102,3041301</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:4000_3041201:1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:5500_3041201:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:10000_3041201:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:6500_3041201:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:7500_3041201:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:8500_3041201:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:5000_3041301:2500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3041501:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同时攻击范围内的所有敌人</t>
+    <t>3050301:3000_3550100:1_3551000:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:4000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每攻击12次释放1次冰霜新星，造成冰元素伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4514,8 +4510,8 @@
       <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>250</v>
+      <c r="E27" s="14">
+        <v>10109011</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -4555,8 +4551,8 @@
       <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>250</v>
+      <c r="E28" s="14">
+        <v>10109012</v>
       </c>
       <c r="F28" s="15">
         <v>1</v>
@@ -4565,15 +4561,17 @@
         <v>100</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>575</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>768</v>
-      </c>
-      <c r="K28" s="15"/>
+        <v>576</v>
+      </c>
+      <c r="K28" s="15">
+        <v>3041501</v>
+      </c>
       <c r="L28" s="15" t="s">
         <v>605</v>
       </c>
@@ -8089,7 +8087,7 @@
         <v>500</v>
       </c>
       <c r="H114" s="20" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="I114" s="20" t="s">
         <v>393</v>
@@ -8136,7 +8134,7 @@
         <v>656</v>
       </c>
       <c r="J115" s="20" t="s">
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="K115" s="20"/>
       <c r="L115" s="20" t="s">
@@ -8169,7 +8167,7 @@
         <v>500</v>
       </c>
       <c r="H116" s="20" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="I116" s="20" t="s">
         <v>395</v>
@@ -8210,7 +8208,7 @@
         <v>500</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="I117" s="20" t="s">
         <v>396</v>
@@ -8251,7 +8249,7 @@
         <v>500</v>
       </c>
       <c r="H118" s="20" t="s">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="I118" s="20" t="s">
         <v>397</v>
@@ -8292,7 +8290,7 @@
         <v>500</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="I119" s="20" t="s">
         <v>398</v>
@@ -8327,7 +8325,7 @@
         <v>900010805</v>
       </c>
       <c r="F120" s="20">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G120" s="20">
         <v>500</v>
@@ -9629,16 +9627,16 @@
         <v>500</v>
       </c>
       <c r="H152" s="39" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="I152" s="37" t="s">
         <v>536</v>
       </c>
       <c r="J152" s="37" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="K152" s="39" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="L152" s="37" t="s">
         <v>605</v>
@@ -9670,16 +9668,16 @@
         <v>500</v>
       </c>
       <c r="H153" s="39" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="I153" s="37" t="s">
         <v>537</v>
       </c>
       <c r="J153" s="37" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="K153" s="39" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="L153" s="37" t="s">
         <v>606</v>
@@ -9711,7 +9709,7 @@
         <v>500</v>
       </c>
       <c r="H154" s="39" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="I154" s="37" t="s">
         <v>538</v>
@@ -9750,7 +9748,7 @@
         <v>500</v>
       </c>
       <c r="H155" s="39" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="I155" s="37" t="s">
         <v>539</v>
@@ -9789,7 +9787,7 @@
         <v>500</v>
       </c>
       <c r="H156" s="39" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="I156" s="37" t="s">
         <v>540</v>
@@ -9828,7 +9826,7 @@
         <v>500</v>
       </c>
       <c r="H157" s="39" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="I157" s="37" t="s">
         <v>542</v>
@@ -9867,7 +9865,7 @@
         <v>500</v>
       </c>
       <c r="H158" s="39" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="I158" s="37" t="s">
         <v>544</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_v8【迷宫-能力词条】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_v8【迷宫-能力词条】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A7E337-076B-4970-BBB8-23FCBC5D7E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8226C3-1AA4-4FB7-BDCD-9FEA3B28630D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="792">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1527,261 +1527,6 @@
     <t>冰霜终结</t>
   </si>
   <si>
-    <t>3040102:3000</t>
-  </si>
-  <si>
-    <t>3040102:5000</t>
-  </si>
-  <si>
-    <t>3040102:7000</t>
-  </si>
-  <si>
-    <t>3040102:10000</t>
-  </si>
-  <si>
-    <t>3040102:15000</t>
-  </si>
-  <si>
-    <t>3040301:3000</t>
-  </si>
-  <si>
-    <t>3040301:5000</t>
-  </si>
-  <si>
-    <t>3040301:7000</t>
-  </si>
-  <si>
-    <t>3040301:10000</t>
-  </si>
-  <si>
-    <t>3040301:15000</t>
-  </si>
-  <si>
-    <t>3040701:3000</t>
-  </si>
-  <si>
-    <t>3040701:5000</t>
-  </si>
-  <si>
-    <t>3040701:7000</t>
-  </si>
-  <si>
-    <t>3040701:10000</t>
-  </si>
-  <si>
-    <t>3040701:15000</t>
-  </si>
-  <si>
-    <t>3041001:3000</t>
-  </si>
-  <si>
-    <t>3041001:5000</t>
-  </si>
-  <si>
-    <t>3041001:7000</t>
-  </si>
-  <si>
-    <t>3041001:10000</t>
-  </si>
-  <si>
-    <t>3041001:15000</t>
-  </si>
-  <si>
-    <t>3041301:3000</t>
-  </si>
-  <si>
-    <t>3041301:5000</t>
-  </si>
-  <si>
-    <t>3041301:7000</t>
-  </si>
-  <si>
-    <t>3041301:10000</t>
-  </si>
-  <si>
-    <t>3041301:15000</t>
-  </si>
-  <si>
-    <t>3050001:3000_3050000:1</t>
-  </si>
-  <si>
-    <t>3050001:5000_3050000:1</t>
-  </si>
-  <si>
-    <t>3050001:7000_3050000:1</t>
-  </si>
-  <si>
-    <t>3050001:10000_3050000:1</t>
-  </si>
-  <si>
-    <t>3050001:15000_3050000:1</t>
-  </si>
-  <si>
-    <t>3050102:3000</t>
-  </si>
-  <si>
-    <t>3050102:5000</t>
-  </si>
-  <si>
-    <t>3050102:7000</t>
-  </si>
-  <si>
-    <t>3050102:10000</t>
-  </si>
-  <si>
-    <t>3050102:15000</t>
-  </si>
-  <si>
-    <t>3050301:3000</t>
-  </si>
-  <si>
-    <t>3050301:5000</t>
-  </si>
-  <si>
-    <t>3050301:7000</t>
-  </si>
-  <si>
-    <t>3050301:10000</t>
-  </si>
-  <si>
-    <t>3050301:15000</t>
-  </si>
-  <si>
-    <t>3060001:3000_3060000:1</t>
-  </si>
-  <si>
-    <t>3060001:5000_3060000:1</t>
-  </si>
-  <si>
-    <t>3060001:7000_3060000:1</t>
-  </si>
-  <si>
-    <t>3060001:10000_3060000:1</t>
-  </si>
-  <si>
-    <t>3060001:15000_3060000:1</t>
-  </si>
-  <si>
-    <t>3060102:3000</t>
-  </si>
-  <si>
-    <t>3060102:5000</t>
-  </si>
-  <si>
-    <t>3060102:7000</t>
-  </si>
-  <si>
-    <t>3060102:10000</t>
-  </si>
-  <si>
-    <t>3060102:15000</t>
-  </si>
-  <si>
-    <t>3060301:3000</t>
-  </si>
-  <si>
-    <t>3060301:5000</t>
-  </si>
-  <si>
-    <t>3060301:7000</t>
-  </si>
-  <si>
-    <t>3060301:10000</t>
-  </si>
-  <si>
-    <t>3060301:15000</t>
-  </si>
-  <si>
-    <t>3070001:3000_3070000:1</t>
-  </si>
-  <si>
-    <t>3070001:5000_3070000:1</t>
-  </si>
-  <si>
-    <t>3070001:7000_3070000:1</t>
-  </si>
-  <si>
-    <t>3070001:10000_3070000:1</t>
-  </si>
-  <si>
-    <t>3070001:15000_3070000:1</t>
-  </si>
-  <si>
-    <t>3070102:3000</t>
-  </si>
-  <si>
-    <t>3070102:5000</t>
-  </si>
-  <si>
-    <t>3070102:7000</t>
-  </si>
-  <si>
-    <t>3070102:10000</t>
-  </si>
-  <si>
-    <t>3070102:15000</t>
-  </si>
-  <si>
-    <t>3070301:3000</t>
-  </si>
-  <si>
-    <t>3070301:5000</t>
-  </si>
-  <si>
-    <t>3070301:7000</t>
-  </si>
-  <si>
-    <t>3070301:10000</t>
-  </si>
-  <si>
-    <t>3070301:15000</t>
-  </si>
-  <si>
-    <t>3080001:3000_3080000:1</t>
-  </si>
-  <si>
-    <t>3080001:5000_3080000:1</t>
-  </si>
-  <si>
-    <t>3080001:7000_3080000:1</t>
-  </si>
-  <si>
-    <t>3080001:10000_3080000:1</t>
-  </si>
-  <si>
-    <t>3080001:15000_3080000:1</t>
-  </si>
-  <si>
-    <t>3080102:3000</t>
-  </si>
-  <si>
-    <t>3080102:5000</t>
-  </si>
-  <si>
-    <t>3080102:7000</t>
-  </si>
-  <si>
-    <t>3080102:10000</t>
-  </si>
-  <si>
-    <t>3080102:15000</t>
-  </si>
-  <si>
-    <t>3080301:3000</t>
-  </si>
-  <si>
-    <t>3080301:5000</t>
-  </si>
-  <si>
-    <t>3080301:7000</t>
-  </si>
-  <si>
-    <t>3080301:10000</t>
-  </si>
-  <si>
-    <t>3080301:15000</t>
-  </si>
-  <si>
     <t>强化陨石</t>
   </si>
   <si>
@@ -1888,18 +1633,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3040202:2000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040901:1500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3041201:1500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>燃烧时死亡，对周围同伴造成自身最大生命50%的火元素伤害，并使目标燃烧。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2004,10 +1737,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每层狂暴状态会使自身暴击伤害+10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>强化致命暴击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2111,10 +1840,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3040202:2000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>906010202</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2127,14 +1852,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3040202:1500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3041102:2000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1011001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2187,54 +1904,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3041501:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3070102:10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3070102:20000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3070102:30000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3070102:40000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3070102:50000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3080102:20000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3080102:30000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3080102:40000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3080102:50000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3041001:3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>affix_icon_atlas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2307,42 +1980,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3540100:1</t>
-  </si>
-  <si>
-    <t>3540300:1</t>
-  </si>
-  <si>
-    <t>3540500:1</t>
-  </si>
-  <si>
-    <t>3540700:1</t>
-  </si>
-  <si>
-    <t>3540900:1</t>
-  </si>
-  <si>
-    <t>3541100:1</t>
-  </si>
-  <si>
-    <t>3541300:1</t>
-  </si>
-  <si>
-    <t>3541500:1</t>
-  </si>
-  <si>
-    <t>3541700:1</t>
-  </si>
-  <si>
-    <t>3541900:1</t>
-  </si>
-  <si>
-    <t>3542100:1</t>
-  </si>
-  <si>
-    <t>3542300:1</t>
-  </si>
-  <si>
     <t>攻击速度提高5%，持续4秒，最多叠加3层</t>
   </si>
   <si>
@@ -2376,38 +2013,6 @@
     <t>移动速度提高5%，持续4秒，最多叠加3层</t>
   </si>
   <si>
-    <t>3040102:5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:7000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:4000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3060001:4000_3060000:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3060102:12500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3060102:15000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3060102:17500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>受到伤害提高5%，持续4秒，最多叠加3层</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2415,24 +2020,15 @@
     <t>攻击时附带%s的冰元素伤害</t>
   </si>
   <si>
-    <t>3550400:1</t>
-  </si>
-  <si>
     <t>冰霜新星</t>
   </si>
   <si>
     <t>冰元素伤害+%s，攻击冰冻的目标时造成额外10%%最大生命值的伤害</t>
   </si>
   <si>
-    <t>3550501:3_3551400:1</t>
-  </si>
-  <si>
     <t>释放冰霜新星需要的攻击-%s次，冰霜新星的冰冻的几率+20%%</t>
   </si>
   <si>
-    <t>3550206:1500_3550800:1</t>
-  </si>
-  <si>
     <t>冰冻几率+%s，对已经处于冰冻的目标再次触发冰冻时造成30%%攻击的伤害。</t>
   </si>
   <si>
@@ -2442,171 +2038,102 @@
     <t>冰冻几率+%s，冰冻时间+%s秒，攻击冰冻目标被会造成50%%的额外伤害。</t>
   </si>
   <si>
-    <t>3060001:4000_3060000:1</t>
-  </si>
-  <si>
     <t>攻击时附带%s的火元素伤害</t>
   </si>
   <si>
-    <t>3060301:12500_3560100:1</t>
-  </si>
-  <si>
-    <t>3060102:15000_3560400:1</t>
-  </si>
-  <si>
-    <t>3060701:17500_3560600:1</t>
-  </si>
-  <si>
-    <t>3560501:3_3560800:1</t>
-  </si>
-  <si>
-    <t>3060701:17500_3561300:1</t>
-  </si>
-  <si>
     <t>燃烧伤害+%s，燃烧时被攻击会受到35%%%攻击力的额外伤害。</t>
   </si>
   <si>
-    <t>3060301:17500_3560503:1</t>
-  </si>
-  <si>
     <t>火元素伤害+%s，陨石释放次数+1。</t>
   </si>
   <si>
-    <t>3060102:17500_3561000:1</t>
-  </si>
-  <si>
     <t>雷电之刃</t>
   </si>
   <si>
     <t>攻击时附带攻击%s的电元素伤害</t>
   </si>
   <si>
-    <t>3070301:10000_3570100:1</t>
-  </si>
-  <si>
     <t>触电</t>
   </si>
   <si>
     <t>电元素伤害+%s，攻击有15%%几率使目标触电。触电状态下，被攻击会受到35%%攻击的触电伤害，触电状态持续5秒。</t>
   </si>
   <si>
-    <t>3570600:1_3570400:1</t>
-  </si>
-  <si>
     <t>闪电链</t>
   </si>
   <si>
     <t>每8次攻击释放1次闪电链，对周围任意目标造成150%攻击力的电元素伤害，并弹射3次，每次弹射会使伤害降低25%。</t>
   </si>
   <si>
-    <t>3070301:10000_3570800:1</t>
-  </si>
-  <si>
     <t>强化触电</t>
   </si>
   <si>
     <t>电元素伤害+%s，触电时受到伤害提高20%%</t>
   </si>
   <si>
-    <t>3570701:3_3570503:2500</t>
-  </si>
-  <si>
     <t>强化闪电链</t>
   </si>
   <si>
-    <t>3571000:1_3570201:3000</t>
-  </si>
-  <si>
     <t>双重触电</t>
   </si>
   <si>
     <t>触电伤害+%s，攻击使目标触电时会立刻触发1次触电伤害</t>
   </si>
   <si>
-    <t>3070301:40000_3570703:1</t>
-  </si>
-  <si>
     <t>双重闪电链</t>
   </si>
   <si>
     <t>电元素伤害+%s，闪电链的释放次数+1</t>
   </si>
   <si>
-    <t>3570201:30000_3571200:1</t>
-  </si>
-  <si>
     <t>电磁爆炸</t>
   </si>
   <si>
     <t>触电伤害+300%，触电伤害范围扩大，并使受到伤害的目标触电。</t>
   </si>
   <si>
-    <t>3080001:3000_3080000:1_3580100:1</t>
-  </si>
-  <si>
     <t>枯木之刃</t>
   </si>
   <si>
     <t>攻击时附带攻击%s的毒元素伤害，攻击有15%%几率使目标中毒。中毒的目标每秒受到20%%攻击力的中毒伤害，中毒持续20秒。</t>
   </si>
   <si>
-    <t>3080301:10000_3080701:4000</t>
-  </si>
-  <si>
     <t>剧毒</t>
   </si>
   <si>
     <t>毒元素伤害+%s，中毒伤害+%s</t>
   </si>
   <si>
-    <t>3580400:1</t>
-  </si>
-  <si>
     <t>传染</t>
   </si>
   <si>
     <t>每8次攻击释放1次中毒传染，对周围造成150%攻击力的毒元素伤害，并使目标中毒。</t>
   </si>
   <si>
-    <t>3080701:5000_3580600:1</t>
-  </si>
-  <si>
     <t>强化剧毒</t>
   </si>
   <si>
     <t>中毒伤害+%s，中毒的目标再次中毒时立刻受到5次中毒伤害。</t>
   </si>
   <si>
-    <t>3580501:3_3580207:1</t>
-  </si>
-  <si>
     <t>强化传染</t>
   </si>
   <si>
     <t>释放中毒传染需要的攻击-%s次，中毒状态可以叠加2层。</t>
   </si>
   <si>
-    <t>3080701:6000_3580800:1</t>
-  </si>
-  <si>
     <t>死亡传染</t>
   </si>
   <si>
     <t>中毒伤害+%s，中毒时死亡会使附近任意怪物获得1层瘟疫。瘟疫中的目标每秒受到20%%攻击力的中毒伤害，持续20秒，最多可叠加10层。</t>
   </si>
   <si>
-    <t>3080301:40000_3580503:1</t>
-  </si>
-  <si>
     <t>双重传染</t>
   </si>
   <si>
     <t>毒元素伤害+%s，中毒传染释放次数+1</t>
   </si>
   <si>
-    <t>3080301:50000_3580208:6700</t>
-  </si>
-  <si>
     <t>极速腐化</t>
   </si>
   <si>
@@ -2645,34 +2172,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3550206:1500_3551200:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:8000</t>
-  </si>
-  <si>
-    <t>3040102:9000</t>
-  </si>
-  <si>
-    <t>3040102:11000</t>
-  </si>
-  <si>
-    <t>3040102:12000</t>
-  </si>
-  <si>
-    <t>3060102:20000</t>
-  </si>
-  <si>
-    <t>3060102:22500</t>
-  </si>
-  <si>
-    <t>3060102:25000</t>
-  </si>
-  <si>
-    <t>3060102:27500</t>
-  </si>
-  <si>
     <t>冰元素伤害+%s，攻击有15%%几率使目标冰冻，同时受到冰元素伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2681,37 +2180,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3050001:4000_3050000:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:10000_3550100:1_3551000:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:10000_3551101:100000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:10000_3550703:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3550206,3551200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3050301:20000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>强化冰霜伤害</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3050001:4000_3050000:1</t>
-  </si>
-  <si>
     <t>冰元素伤害+%s，攻击有几率使目标冰冻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2720,10 +2196,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3050301:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3040102,3041201</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2740,55 +2212,641 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3040102:4000_3041201:1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:5500_3041201:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:10000_3041201:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:6500_3041201:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:7500_3041201:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:8500_3041201:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:5000_3041301:2500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3041501:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3550501:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:3000_3550100:1_3551000:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:4000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>每攻击12次释放1次冰霜新星，造成冰元素伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化锐眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040202:1500_9201:3000</t>
+  </si>
+  <si>
+    <t>3040301:3000_9201:5000</t>
+  </si>
+  <si>
+    <t>3040301:5000_9201:7000</t>
+  </si>
+  <si>
+    <t>3040301:7000_9201:10000</t>
+  </si>
+  <si>
+    <t>3040301:10000_9201:15000</t>
+  </si>
+  <si>
+    <t>3040301:15000_9201:3000</t>
+  </si>
+  <si>
+    <t>3040701:3000_9201:5000</t>
+  </si>
+  <si>
+    <t>3040701:5000_9201:7000</t>
+  </si>
+  <si>
+    <t>3040701:7000_9201:10000</t>
+  </si>
+  <si>
+    <t>3040701:10000_9201:15000</t>
+  </si>
+  <si>
+    <t>3040701:15000_9201:3000</t>
+  </si>
+  <si>
+    <t>3040901:1500_9201:5000</t>
+  </si>
+  <si>
+    <t>3040901:1500_9201:7000</t>
+  </si>
+  <si>
+    <t>3040901:1500_9201:10000</t>
+  </si>
+  <si>
+    <t>3040901:1500_9201:15000</t>
+  </si>
+  <si>
+    <t>3040901:1500_9201:3000</t>
+  </si>
+  <si>
+    <t>3040102:7000_9201:7000</t>
+  </si>
+  <si>
+    <t>3041001:3000_9201:10000</t>
+  </si>
+  <si>
+    <t>3041001:5000_9201:15000</t>
+  </si>
+  <si>
+    <t>3041001:7000_9201:3000</t>
+  </si>
+  <si>
+    <t>3041001:10000_9201:5000</t>
+  </si>
+  <si>
+    <t>3041001:15000_9201:7000</t>
+  </si>
+  <si>
+    <t>3041201:1500_9201:10000</t>
+  </si>
+  <si>
+    <t>3041201:1500_9201:15000</t>
+  </si>
+  <si>
+    <t>3041201:1500_9201:3000</t>
+  </si>
+  <si>
+    <t>3041201:1500_9201:5000</t>
+  </si>
+  <si>
+    <t>3041201:1500_9201:7000</t>
+  </si>
+  <si>
+    <t>3041301:3000_9201:10000</t>
+  </si>
+  <si>
+    <t>3041301:5000_9201:15000</t>
+  </si>
+  <si>
+    <t>3041301:7000_9201:3000</t>
+  </si>
+  <si>
+    <t>3041301:10000_9201:5000</t>
+  </si>
+  <si>
+    <t>3041301:15000_9201:7000</t>
+  </si>
+  <si>
+    <t>3050001:3000_3050000:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3050001:5000_3050000:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3050001:7000_3050000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3050001:10000_3050000:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3050001:15000_3050000:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3050102:3000_9201:10000</t>
+  </si>
+  <si>
+    <t>3050102:5000_9201:15000</t>
+  </si>
+  <si>
+    <t>3050102:7000_9201:3000</t>
+  </si>
+  <si>
+    <t>3050102:10000_9201:5000</t>
+  </si>
+  <si>
+    <t>3050102:15000_9201:7000</t>
+  </si>
+  <si>
+    <t>3050301:3000_9201:10000</t>
+  </si>
+  <si>
+    <t>3050301:5000_9201:15000</t>
+  </si>
+  <si>
+    <t>3050301:7000_9201:3000</t>
+  </si>
+  <si>
+    <t>3050301:10000_9201:5000</t>
+  </si>
+  <si>
+    <t>3050301:15000_9201:7000</t>
+  </si>
+  <si>
+    <t>3060001:3000_3060000:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3060001:5000_3060000:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3060001:7000_3060000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3060001:10000_3060000:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3060001:15000_3060000:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3060102:3000_9201:10000</t>
+  </si>
+  <si>
+    <t>3060102:5000_9201:15000</t>
+  </si>
+  <si>
+    <t>3060102:7000_9201:3000</t>
+  </si>
+  <si>
+    <t>3060102:10000_9201:5000</t>
+  </si>
+  <si>
+    <t>3060102:15000_9201:7000</t>
+  </si>
+  <si>
+    <t>3060301:3000_9201:10000</t>
+  </si>
+  <si>
+    <t>3060301:5000_9201:15000</t>
+  </si>
+  <si>
+    <t>3060301:7000_9201:3000</t>
+  </si>
+  <si>
+    <t>3060301:10000_9201:5000</t>
+  </si>
+  <si>
+    <t>3060301:15000_9201:7000</t>
+  </si>
+  <si>
+    <t>3070001:3000_3070000:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3070001:5000_3070000:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3070001:7000_3070000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3070001:10000_3070000:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3070001:15000_3070000:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3070102:3000_9201:10000</t>
+  </si>
+  <si>
+    <t>3070102:5000_9201:15000</t>
+  </si>
+  <si>
+    <t>3070102:7000_9201:3000</t>
+  </si>
+  <si>
+    <t>3070102:10000_9201:5000</t>
+  </si>
+  <si>
+    <t>3070102:15000_9201:7000</t>
+  </si>
+  <si>
+    <t>3070301:3000_9201:10000</t>
+  </si>
+  <si>
+    <t>3070301:5000_9201:15000</t>
+  </si>
+  <si>
+    <t>3070301:7000_9201:3000</t>
+  </si>
+  <si>
+    <t>3070301:10000_9201:5000</t>
+  </si>
+  <si>
+    <t>3070301:15000_9201:7000</t>
+  </si>
+  <si>
+    <t>3080001:3000_3080000:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3080001:5000_3080000:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3080001:7000_3080000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3080001:10000_3080000:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3080001:15000_3080000:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3080102:3000_9201:10000</t>
+  </si>
+  <si>
+    <t>3080102:5000_9201:15000</t>
+  </si>
+  <si>
+    <t>3080102:7000_9201:3000</t>
+  </si>
+  <si>
+    <t>3080102:10000_9201:5000</t>
+  </si>
+  <si>
+    <t>3080102:15000_9201:7000</t>
+  </si>
+  <si>
+    <t>3080301:3000_9201:10000</t>
+  </si>
+  <si>
+    <t>3080301:5000_9201:15000</t>
+  </si>
+  <si>
+    <t>3080301:7000_9201:3000</t>
+  </si>
+  <si>
+    <t>3080301:10000_9201:5000</t>
+  </si>
+  <si>
+    <t>3080301:15000_9201:7000</t>
+  </si>
+  <si>
+    <t>3050001:4000_3050000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3050301:6000_3550100:1_3551000:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3060001:4000_3060000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3060102:12500_9201:5000</t>
+  </si>
+  <si>
+    <t>3060102:17500_9201:10000</t>
+  </si>
+  <si>
+    <t>3060102:20000_9201:15000</t>
+  </si>
+  <si>
+    <t>3060102:22500_9201:22000</t>
+  </si>
+  <si>
+    <t>3060102:25000_9201:30000</t>
+  </si>
+  <si>
+    <t>3060102:27500_9201:40000</t>
+  </si>
+  <si>
+    <t>3070001:3000_3070000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3070102:10000_9201:7000</t>
+  </si>
+  <si>
+    <t>3070102:10000_9201:10000</t>
+  </si>
+  <si>
+    <t>3070102:20000_9201:15000</t>
+  </si>
+  <si>
+    <t>3070102:30000_9201:22000</t>
+  </si>
+  <si>
+    <t>3070102:40000_9201:30000</t>
+  </si>
+  <si>
+    <t>3070102:50000_9201:40000</t>
+  </si>
+  <si>
+    <t>3080001:3000_3080000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3080102:10000_9201:7000</t>
+  </si>
+  <si>
+    <t>3080102:10000_9201:10000</t>
+  </si>
+  <si>
+    <t>3080102:20000_9201:15000</t>
+  </si>
+  <si>
+    <t>3080102:30000_9201:22000</t>
+  </si>
+  <si>
+    <t>3080102:40000_9201:30000</t>
+  </si>
+  <si>
+    <t>3080102:50000_9201:40000</t>
+  </si>
+  <si>
+    <t>3040202:2000_9201:3000</t>
+  </si>
+  <si>
+    <t>3041102:2000_9201:5000</t>
+  </si>
+  <si>
+    <t>3041102:2000_9201:7000</t>
+  </si>
+  <si>
+    <t>3040202:2000_9201:10000</t>
+  </si>
+  <si>
+    <t>3041102:2000_9201:15000</t>
+  </si>
+  <si>
+    <t>3040202:2000_9201:22000</t>
+  </si>
+  <si>
+    <t>3040102:4000_9201:30000</t>
+  </si>
+  <si>
+    <t>3040102:4000_3041201:1000_9201:5000</t>
+  </si>
+  <si>
+    <t>3041001:3000_9201:3000</t>
+  </si>
+  <si>
+    <t>3041001:3000_9201:5000</t>
+  </si>
+  <si>
+    <t>3041001:5000_9201:7000</t>
+  </si>
+  <si>
+    <t>3041001:5000_9201:10000</t>
+  </si>
+  <si>
+    <t>3041001:7000_9201:15000</t>
+  </si>
+  <si>
+    <t>3041001:7000_9201:22000</t>
+  </si>
+  <si>
+    <t>3041001:10000_9201:30000</t>
+  </si>
+  <si>
+    <t>3041001:15000_9201:40000</t>
+  </si>
+  <si>
+    <t>3540100:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3540300:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3540500:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3540700:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3540900:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3541100:1_9201:22000</t>
+  </si>
+  <si>
+    <t>3541300:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3541500:1_9201:40000</t>
+  </si>
+  <si>
+    <t>3541700:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3541900:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3542100:1_9201:22000</t>
+  </si>
+  <si>
+    <t>3542300:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3050301:10000_3550100:1_3551000:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3060301:12500_3560100:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3060102:15000_3560400:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3060701:17500_3560600:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3560501:3_3560800:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3060701:17500_3561300:1_9201:22000</t>
+  </si>
+  <si>
+    <t>3060301:17500_3560503:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3060102:17500_3561000:1_9201:40000</t>
+  </si>
+  <si>
+    <t>3070301:10000_3570100:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3570600:1_3570400:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3070301:10000_3570800:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3570701:3_3570503:2500_9201:15000</t>
+  </si>
+  <si>
+    <t>3571000:1_3570201:3000_9201:22000</t>
+  </si>
+  <si>
+    <t>3070301:40000_3570703:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3570201:30000_3571200:1_9201:40000</t>
+  </si>
+  <si>
+    <t>3080001:3000_3080000:1_3580100:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3080301:10000_3080701:4000_9201:5000</t>
+  </si>
+  <si>
+    <t>3580400:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3080701:5000_3580600:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3580501:3_3580207:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3080701:6000_3580800:1_9201:22000</t>
+  </si>
+  <si>
+    <t>3080301:40000_3580503:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3080301:50000_3580208:6700_9201:40000</t>
+  </si>
+  <si>
+    <t>3040102:3000_9201:3000</t>
+  </si>
+  <si>
+    <t>3040102:5000_9201:5000</t>
+  </si>
+  <si>
+    <t>3040102:10000_9201:10000</t>
+  </si>
+  <si>
+    <t>3040102:15000_9201:15000</t>
+  </si>
+  <si>
+    <t>3041501:1_9201:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:5000_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:5000_3041301:2500_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:5000_3041201:500_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:6000_3041201:500_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:7000_3041201:500_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:8000_3041201:500_9201:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:10000_3041201:500_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550400:1_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:10000_3551101:100000_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550501:3_3551400:1_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550206:1500_3550800:1_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:10000_3550703:1_9201:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550206:1500_3551200:1_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:20000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:9000_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550501:2_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:12000_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550501:2_9201:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:15000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3041501:1_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3041501:2_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:4000_9201:5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:6000_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:7000_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:8000_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:9000_9201:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:10000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:11000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:12000_9201:12000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3447,7 +3505,7 @@
     <col min="5" max="5" width="17.25" style="47" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.875" style="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.375" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.375" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="37.875" style="16" customWidth="1"/>
     <col min="11" max="11" width="18.875" style="16" bestFit="1" customWidth="1"/>
@@ -3507,10 +3565,10 @@
         <v>19</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>608</v>
+        <v>505</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>608</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -3548,10 +3606,10 @@
         <v>15</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>601</v>
+        <v>498</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>604</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -3589,10 +3647,10 @@
         <v>11</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>602</v>
+        <v>499</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>603</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3618,7 +3676,7 @@
         <v>100</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>400</v>
+        <v>758</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>132</v>
@@ -3630,7 +3688,7 @@
         <v>3040102</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M5" s="15">
         <v>3600002</v>
@@ -3659,7 +3717,7 @@
         <v>100</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>401</v>
+        <v>759</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>132</v>
@@ -3671,7 +3729,7 @@
         <v>3040102</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M6" s="15">
         <v>3600002</v>
@@ -3700,7 +3758,7 @@
         <v>100</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>402</v>
+        <v>608</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>132</v>
@@ -3712,7 +3770,7 @@
         <v>3040102</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M7" s="15">
         <v>3600002</v>
@@ -3741,7 +3799,7 @@
         <v>100</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>403</v>
+        <v>760</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>132</v>
@@ -3753,7 +3811,7 @@
         <v>3040102</v>
       </c>
       <c r="L8" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M8" s="15">
         <v>3600002</v>
@@ -3782,7 +3840,7 @@
         <v>100</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>404</v>
+        <v>761</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>132</v>
@@ -3794,7 +3852,7 @@
         <v>3040102</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M9" s="15">
         <v>3600002</v>
@@ -3823,7 +3881,7 @@
         <v>100</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>133</v>
@@ -3835,7 +3893,7 @@
         <v>3040202</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M10" s="15">
         <v>3590003</v>
@@ -3864,7 +3922,7 @@
         <v>100</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>405</v>
+        <v>593</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>134</v>
@@ -3876,7 +3934,7 @@
         <v>3040301</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M11" s="15">
         <v>3600002</v>
@@ -3905,7 +3963,7 @@
         <v>100</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>406</v>
+        <v>594</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>134</v>
@@ -3917,7 +3975,7 @@
         <v>3040301</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M12" s="15">
         <v>3600002</v>
@@ -3946,7 +4004,7 @@
         <v>100</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>407</v>
+        <v>595</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>134</v>
@@ -3958,7 +4016,7 @@
         <v>3040301</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M13" s="15">
         <v>3600002</v>
@@ -3987,7 +4045,7 @@
         <v>100</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>408</v>
+        <v>596</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>134</v>
@@ -3999,7 +4057,7 @@
         <v>3040301</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M14" s="15">
         <v>3600002</v>
@@ -4028,7 +4086,7 @@
         <v>100</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>409</v>
+        <v>597</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>134</v>
@@ -4040,7 +4098,7 @@
         <v>3040301</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M15" s="15">
         <v>3600002</v>
@@ -4069,7 +4127,7 @@
         <v>100</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>410</v>
+        <v>598</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>136</v>
@@ -4081,7 +4139,7 @@
         <v>3040701</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M16" s="15">
         <v>3600002</v>
@@ -4110,7 +4168,7 @@
         <v>100</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>411</v>
+        <v>599</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>136</v>
@@ -4122,7 +4180,7 @@
         <v>3040701</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M17" s="15">
         <v>3600002</v>
@@ -4151,7 +4209,7 @@
         <v>100</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>412</v>
+        <v>600</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>136</v>
@@ -4163,7 +4221,7 @@
         <v>3040701</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M18" s="15">
         <v>3600002</v>
@@ -4192,7 +4250,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>413</v>
+        <v>601</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>136</v>
@@ -4204,7 +4262,7 @@
         <v>3040701</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M19" s="15">
         <v>3600002</v>
@@ -4233,7 +4291,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>414</v>
+        <v>602</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>136</v>
@@ -4245,7 +4303,7 @@
         <v>3040701</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M20" s="15">
         <v>3600002</v>
@@ -4274,7 +4332,7 @@
         <v>100</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>513</v>
+        <v>603</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>137</v>
@@ -4286,7 +4344,7 @@
         <v>3040901</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M21" s="15">
         <v>3600004</v>
@@ -4315,7 +4373,7 @@
         <v>100</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>513</v>
+        <v>604</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>137</v>
@@ -4327,7 +4385,7 @@
         <v>3040901</v>
       </c>
       <c r="L22" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M22" s="15">
         <v>3600004</v>
@@ -4356,7 +4414,7 @@
         <v>100</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>513</v>
+        <v>605</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>137</v>
@@ -4368,7 +4426,7 @@
         <v>3040901</v>
       </c>
       <c r="L23" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M23" s="15">
         <v>3600004</v>
@@ -4397,7 +4455,7 @@
         <v>100</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>513</v>
+        <v>606</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>137</v>
@@ -4409,7 +4467,7 @@
         <v>3040901</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M24" s="15">
         <v>3600004</v>
@@ -4438,7 +4496,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>513</v>
+        <v>607</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>137</v>
@@ -4450,7 +4508,7 @@
         <v>3040901</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M25" s="15">
         <v>3600004</v>
@@ -4479,19 +4537,19 @@
         <v>100</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>589</v>
+        <v>762</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>576</v>
+        <v>484</v>
       </c>
       <c r="K26" s="15">
         <v>3041501</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M26" s="15">
         <v>3610003</v>
@@ -4520,19 +4578,19 @@
         <v>100</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>589</v>
+        <v>782</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>576</v>
+        <v>484</v>
       </c>
       <c r="K27" s="15">
         <v>3041501</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M27" s="15">
         <v>3610003</v>
@@ -4561,19 +4619,19 @@
         <v>100</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>762</v>
+        <v>783</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>576</v>
+        <v>484</v>
       </c>
       <c r="K28" s="15">
         <v>3041501</v>
       </c>
       <c r="L28" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M28" s="15">
         <v>3610003</v>
@@ -4602,10 +4660,10 @@
         <v>100</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>648</v>
+        <v>784</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>599</v>
+        <v>497</v>
       </c>
       <c r="J29" s="15" t="s">
         <v>6</v>
@@ -4614,7 +4672,7 @@
         <v>3040102</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M29" s="15">
         <v>3600002</v>
@@ -4643,10 +4701,10 @@
         <v>100</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>645</v>
+        <v>763</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>599</v>
+        <v>497</v>
       </c>
       <c r="J30" s="15" t="s">
         <v>6</v>
@@ -4655,7 +4713,7 @@
         <v>3040102</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M30" s="15">
         <v>3600002</v>
@@ -4684,10 +4742,10 @@
         <v>100</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>646</v>
+        <v>785</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>599</v>
+        <v>497</v>
       </c>
       <c r="J31" s="15" t="s">
         <v>6</v>
@@ -4696,7 +4754,7 @@
         <v>3040102</v>
       </c>
       <c r="L31" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M31" s="15">
         <v>3600002</v>
@@ -4725,10 +4783,10 @@
         <v>100</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>647</v>
+        <v>786</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>599</v>
+        <v>497</v>
       </c>
       <c r="J32" s="15" t="s">
         <v>6</v>
@@ -4737,7 +4795,7 @@
         <v>3040102</v>
       </c>
       <c r="L32" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M32" s="15">
         <v>3600002</v>
@@ -4766,10 +4824,10 @@
         <v>100</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>730</v>
+        <v>787</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>599</v>
+        <v>497</v>
       </c>
       <c r="J33" s="15" t="s">
         <v>6</v>
@@ -4778,7 +4836,7 @@
         <v>3040102</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M33" s="15">
         <v>3600002</v>
@@ -4807,10 +4865,10 @@
         <v>100</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>731</v>
+        <v>788</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>599</v>
+        <v>497</v>
       </c>
       <c r="J34" s="15" t="s">
         <v>6</v>
@@ -4819,7 +4877,7 @@
         <v>3040102</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M34" s="15">
         <v>3600002</v>
@@ -4848,10 +4906,10 @@
         <v>100</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>403</v>
+        <v>789</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>599</v>
+        <v>497</v>
       </c>
       <c r="J35" s="15" t="s">
         <v>6</v>
@@ -4860,7 +4918,7 @@
         <v>3040102</v>
       </c>
       <c r="L35" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M35" s="15">
         <v>3600002</v>
@@ -4889,10 +4947,10 @@
         <v>100</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>732</v>
+        <v>790</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>599</v>
+        <v>497</v>
       </c>
       <c r="J36" s="15" t="s">
         <v>6</v>
@@ -4901,7 +4959,7 @@
         <v>3040102</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M36" s="15">
         <v>3600002</v>
@@ -4930,10 +4988,10 @@
         <v>100</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>733</v>
+        <v>791</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>599</v>
+        <v>497</v>
       </c>
       <c r="J37" s="15" t="s">
         <v>6</v>
@@ -4942,7 +5000,7 @@
         <v>3040102</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M37" s="15">
         <v>3600002</v>
@@ -4971,7 +5029,7 @@
         <v>100</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>138</v>
@@ -4983,7 +5041,7 @@
         <v>3041001</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M38" s="15">
         <v>3610001</v>
@@ -5003,7 +5061,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>574</v>
+        <v>482</v>
       </c>
       <c r="F39" s="15">
         <v>1</v>
@@ -5012,7 +5070,7 @@
         <v>100</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>416</v>
+        <v>610</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>138</v>
@@ -5024,7 +5082,7 @@
         <v>3041001</v>
       </c>
       <c r="L39" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M39" s="15">
         <v>3610001</v>
@@ -5053,7 +5111,7 @@
         <v>100</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>417</v>
+        <v>611</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>138</v>
@@ -5065,7 +5123,7 @@
         <v>3041001</v>
       </c>
       <c r="L40" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M40" s="15">
         <v>3610001</v>
@@ -5094,7 +5152,7 @@
         <v>100</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>418</v>
+        <v>612</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>138</v>
@@ -5106,7 +5164,7 @@
         <v>3041001</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M41" s="15">
         <v>3610001</v>
@@ -5135,7 +5193,7 @@
         <v>100</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>419</v>
+        <v>613</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>138</v>
@@ -5147,7 +5205,7 @@
         <v>3041001</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M42" s="15">
         <v>3610001</v>
@@ -5176,7 +5234,7 @@
         <v>100</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>514</v>
+        <v>614</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>140</v>
@@ -5188,7 +5246,7 @@
         <v>3041201</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M43" s="15">
         <v>3600003</v>
@@ -5217,7 +5275,7 @@
         <v>100</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>514</v>
+        <v>615</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>140</v>
@@ -5229,7 +5287,7 @@
         <v>3041201</v>
       </c>
       <c r="L44" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M44" s="15">
         <v>3600003</v>
@@ -5258,7 +5316,7 @@
         <v>100</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>514</v>
+        <v>616</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>140</v>
@@ -5270,7 +5328,7 @@
         <v>3041201</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M45" s="15">
         <v>3600003</v>
@@ -5299,7 +5357,7 @@
         <v>100</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>514</v>
+        <v>617</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>140</v>
@@ -5311,7 +5369,7 @@
         <v>3041201</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M46" s="15">
         <v>3600003</v>
@@ -5340,7 +5398,7 @@
         <v>100</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>514</v>
+        <v>618</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>140</v>
@@ -5352,7 +5410,7 @@
         <v>3041201</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M47" s="15">
         <v>3600003</v>
@@ -5381,7 +5439,7 @@
         <v>100</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>420</v>
+        <v>619</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>141</v>
@@ -5393,7 +5451,7 @@
         <v>3041301</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M48" s="15">
         <v>3600003</v>
@@ -5422,7 +5480,7 @@
         <v>100</v>
       </c>
       <c r="H49" s="18" t="s">
-        <v>421</v>
+        <v>620</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>141</v>
@@ -5434,7 +5492,7 @@
         <v>3041301</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M49" s="15">
         <v>3600003</v>
@@ -5463,7 +5521,7 @@
         <v>100</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>422</v>
+        <v>621</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>141</v>
@@ -5475,7 +5533,7 @@
         <v>3041301</v>
       </c>
       <c r="L50" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M50" s="15">
         <v>3600003</v>
@@ -5504,7 +5562,7 @@
         <v>100</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>423</v>
+        <v>622</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>141</v>
@@ -5516,7 +5574,7 @@
         <v>3041301</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M51" s="15">
         <v>3600003</v>
@@ -5545,7 +5603,7 @@
         <v>100</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>424</v>
+        <v>623</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>141</v>
@@ -5557,7 +5615,7 @@
         <v>3041301</v>
       </c>
       <c r="L52" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M52" s="15">
         <v>3600003</v>
@@ -5586,7 +5644,7 @@
         <v>100</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>425</v>
+        <v>624</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>143</v>
@@ -5598,7 +5656,7 @@
         <v>3050001</v>
       </c>
       <c r="L53" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M53" s="15">
         <v>3550001</v>
@@ -5627,7 +5685,7 @@
         <v>100</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>426</v>
+        <v>625</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>143</v>
@@ -5639,7 +5697,7 @@
         <v>3050001</v>
       </c>
       <c r="L54" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M54" s="15">
         <v>3550001</v>
@@ -5668,7 +5726,7 @@
         <v>100</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>427</v>
+        <v>626</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>143</v>
@@ -5680,7 +5738,7 @@
         <v>3050001</v>
       </c>
       <c r="L55" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M55" s="15">
         <v>3550001</v>
@@ -5709,7 +5767,7 @@
         <v>100</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>428</v>
+        <v>627</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>143</v>
@@ -5721,7 +5779,7 @@
         <v>3050001</v>
       </c>
       <c r="L56" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M56" s="15">
         <v>3550001</v>
@@ -5750,7 +5808,7 @@
         <v>100</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>429</v>
+        <v>628</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>143</v>
@@ -5762,7 +5820,7 @@
         <v>3050001</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M57" s="15">
         <v>3550001</v>
@@ -5791,7 +5849,7 @@
         <v>100</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>430</v>
+        <v>629</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>144</v>
@@ -5803,7 +5861,7 @@
         <v>3050102</v>
       </c>
       <c r="L58" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M58" s="15">
         <v>3550001</v>
@@ -5832,7 +5890,7 @@
         <v>100</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>431</v>
+        <v>630</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>144</v>
@@ -5844,7 +5902,7 @@
         <v>3050102</v>
       </c>
       <c r="L59" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M59" s="15">
         <v>3550001</v>
@@ -5873,7 +5931,7 @@
         <v>100</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>432</v>
+        <v>631</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>144</v>
@@ -5885,7 +5943,7 @@
         <v>3050102</v>
       </c>
       <c r="L60" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M60" s="15">
         <v>3550001</v>
@@ -5914,7 +5972,7 @@
         <v>100</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>433</v>
+        <v>632</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>144</v>
@@ -5926,7 +5984,7 @@
         <v>3050102</v>
       </c>
       <c r="L61" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M61" s="15">
         <v>3550001</v>
@@ -5955,7 +6013,7 @@
         <v>100</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>434</v>
+        <v>633</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>144</v>
@@ -5967,7 +6025,7 @@
         <v>3050102</v>
       </c>
       <c r="L62" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M62" s="15">
         <v>3550001</v>
@@ -5996,7 +6054,7 @@
         <v>100</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>435</v>
+        <v>634</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>145</v>
@@ -6008,7 +6066,7 @@
         <v>3050301</v>
       </c>
       <c r="L63" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M63" s="15">
         <v>3550001</v>
@@ -6037,7 +6095,7 @@
         <v>100</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>436</v>
+        <v>635</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>145</v>
@@ -6049,7 +6107,7 @@
         <v>3050301</v>
       </c>
       <c r="L64" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M64" s="15">
         <v>3550001</v>
@@ -6078,7 +6136,7 @@
         <v>100</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>437</v>
+        <v>636</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>145</v>
@@ -6090,7 +6148,7 @@
         <v>3050301</v>
       </c>
       <c r="L65" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M65" s="15">
         <v>3550001</v>
@@ -6119,7 +6177,7 @@
         <v>100</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>438</v>
+        <v>637</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>145</v>
@@ -6131,7 +6189,7 @@
         <v>3050301</v>
       </c>
       <c r="L66" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M66" s="15">
         <v>3550001</v>
@@ -6160,7 +6218,7 @@
         <v>100</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>439</v>
+        <v>638</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>145</v>
@@ -6172,7 +6230,7 @@
         <v>3050301</v>
       </c>
       <c r="L67" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M67" s="15">
         <v>3550001</v>
@@ -6201,7 +6259,7 @@
         <v>100</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>440</v>
+        <v>639</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>147</v>
@@ -6213,7 +6271,7 @@
         <v>3060001</v>
       </c>
       <c r="L68" s="15" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M68" s="15">
         <v>3560001</v>
@@ -6242,7 +6300,7 @@
         <v>100</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>441</v>
+        <v>640</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>147</v>
@@ -6254,7 +6312,7 @@
         <v>3060001</v>
       </c>
       <c r="L69" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M69" s="15">
         <v>3560001</v>
@@ -6283,7 +6341,7 @@
         <v>100</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>442</v>
+        <v>641</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>147</v>
@@ -6295,7 +6353,7 @@
         <v>3060001</v>
       </c>
       <c r="L70" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M70" s="15">
         <v>3560001</v>
@@ -6324,7 +6382,7 @@
         <v>100</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>443</v>
+        <v>642</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>147</v>
@@ -6336,7 +6394,7 @@
         <v>3060001</v>
       </c>
       <c r="L71" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M71" s="15">
         <v>3560001</v>
@@ -6365,7 +6423,7 @@
         <v>100</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>444</v>
+        <v>643</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>147</v>
@@ -6377,7 +6435,7 @@
         <v>3060001</v>
       </c>
       <c r="L72" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M72" s="15">
         <v>3560001</v>
@@ -6406,7 +6464,7 @@
         <v>100</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>445</v>
+        <v>644</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>81</v>
@@ -6418,7 +6476,7 @@
         <v>3060102</v>
       </c>
       <c r="L73" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M73" s="15">
         <v>3560001</v>
@@ -6447,7 +6505,7 @@
         <v>100</v>
       </c>
       <c r="H74" s="18" t="s">
-        <v>446</v>
+        <v>645</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>81</v>
@@ -6459,7 +6517,7 @@
         <v>3060102</v>
       </c>
       <c r="L74" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M74" s="15">
         <v>3560001</v>
@@ -6488,7 +6546,7 @@
         <v>100</v>
       </c>
       <c r="H75" s="18" t="s">
-        <v>447</v>
+        <v>646</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>81</v>
@@ -6500,7 +6558,7 @@
         <v>3060102</v>
       </c>
       <c r="L75" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M75" s="15">
         <v>3560001</v>
@@ -6529,7 +6587,7 @@
         <v>100</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>448</v>
+        <v>647</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>81</v>
@@ -6541,7 +6599,7 @@
         <v>3060102</v>
       </c>
       <c r="L76" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M76" s="15">
         <v>3560001</v>
@@ -6570,7 +6628,7 @@
         <v>100</v>
       </c>
       <c r="H77" s="18" t="s">
-        <v>449</v>
+        <v>648</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>81</v>
@@ -6582,7 +6640,7 @@
         <v>3060102</v>
       </c>
       <c r="L77" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M77" s="15">
         <v>3560001</v>
@@ -6611,7 +6669,7 @@
         <v>100</v>
       </c>
       <c r="H78" s="18" t="s">
-        <v>450</v>
+        <v>649</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>82</v>
@@ -6623,7 +6681,7 @@
         <v>3060301</v>
       </c>
       <c r="L78" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M78" s="15">
         <v>3560001</v>
@@ -6652,7 +6710,7 @@
         <v>100</v>
       </c>
       <c r="H79" s="18" t="s">
-        <v>451</v>
+        <v>650</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>82</v>
@@ -6664,7 +6722,7 @@
         <v>3060301</v>
       </c>
       <c r="L79" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M79" s="15">
         <v>3560001</v>
@@ -6693,7 +6751,7 @@
         <v>100</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>452</v>
+        <v>651</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>82</v>
@@ -6705,7 +6763,7 @@
         <v>3060301</v>
       </c>
       <c r="L80" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M80" s="15">
         <v>3560001</v>
@@ -6734,7 +6792,7 @@
         <v>100</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>453</v>
+        <v>652</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>82</v>
@@ -6746,7 +6804,7 @@
         <v>3060301</v>
       </c>
       <c r="L81" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M81" s="15">
         <v>3560001</v>
@@ -6775,7 +6833,7 @@
         <v>100</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>454</v>
+        <v>653</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>82</v>
@@ -6787,7 +6845,7 @@
         <v>3060301</v>
       </c>
       <c r="L82" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M82" s="15">
         <v>3560001</v>
@@ -6816,7 +6874,7 @@
         <v>100</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>455</v>
+        <v>654</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>148</v>
@@ -6828,7 +6886,7 @@
         <v>3070001</v>
       </c>
       <c r="L83" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M83" s="15">
         <v>3570001</v>
@@ -6857,7 +6915,7 @@
         <v>100</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>456</v>
+        <v>655</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>148</v>
@@ -6869,7 +6927,7 @@
         <v>3070001</v>
       </c>
       <c r="L84" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M84" s="15">
         <v>3570001</v>
@@ -6898,7 +6956,7 @@
         <v>100</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>457</v>
+        <v>656</v>
       </c>
       <c r="I85" s="15" t="s">
         <v>148</v>
@@ -6910,7 +6968,7 @@
         <v>3070001</v>
       </c>
       <c r="L85" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M85" s="15">
         <v>3570001</v>
@@ -6939,7 +6997,7 @@
         <v>100</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>458</v>
+        <v>657</v>
       </c>
       <c r="I86" s="15" t="s">
         <v>148</v>
@@ -6951,7 +7009,7 @@
         <v>3070001</v>
       </c>
       <c r="L86" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M86" s="15">
         <v>3570001</v>
@@ -6980,7 +7038,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>459</v>
+        <v>658</v>
       </c>
       <c r="I87" s="15" t="s">
         <v>148</v>
@@ -6992,7 +7050,7 @@
         <v>3070001</v>
       </c>
       <c r="L87" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M87" s="15">
         <v>3570001</v>
@@ -7021,7 +7079,7 @@
         <v>100</v>
       </c>
       <c r="H88" s="18" t="s">
-        <v>460</v>
+        <v>659</v>
       </c>
       <c r="I88" s="15" t="s">
         <v>87</v>
@@ -7033,7 +7091,7 @@
         <v>3070102</v>
       </c>
       <c r="L88" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M88" s="15">
         <v>3570001</v>
@@ -7062,7 +7120,7 @@
         <v>100</v>
       </c>
       <c r="H89" s="18" t="s">
-        <v>461</v>
+        <v>660</v>
       </c>
       <c r="I89" s="15" t="s">
         <v>87</v>
@@ -7074,7 +7132,7 @@
         <v>3070102</v>
       </c>
       <c r="L89" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M89" s="15">
         <v>3570001</v>
@@ -7103,7 +7161,7 @@
         <v>100</v>
       </c>
       <c r="H90" s="18" t="s">
-        <v>462</v>
+        <v>661</v>
       </c>
       <c r="I90" s="15" t="s">
         <v>87</v>
@@ -7115,7 +7173,7 @@
         <v>3070102</v>
       </c>
       <c r="L90" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M90" s="15">
         <v>3570001</v>
@@ -7144,7 +7202,7 @@
         <v>100</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>463</v>
+        <v>662</v>
       </c>
       <c r="I91" s="15" t="s">
         <v>87</v>
@@ -7156,7 +7214,7 @@
         <v>3070102</v>
       </c>
       <c r="L91" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M91" s="15">
         <v>3570001</v>
@@ -7185,7 +7243,7 @@
         <v>100</v>
       </c>
       <c r="H92" s="18" t="s">
-        <v>464</v>
+        <v>663</v>
       </c>
       <c r="I92" s="15" t="s">
         <v>87</v>
@@ -7197,7 +7255,7 @@
         <v>3070102</v>
       </c>
       <c r="L92" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M92" s="15">
         <v>3570001</v>
@@ -7226,7 +7284,7 @@
         <v>100</v>
       </c>
       <c r="H93" s="18" t="s">
-        <v>465</v>
+        <v>664</v>
       </c>
       <c r="I93" s="15" t="s">
         <v>88</v>
@@ -7238,7 +7296,7 @@
         <v>3070301</v>
       </c>
       <c r="L93" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M93" s="15">
         <v>3570001</v>
@@ -7267,7 +7325,7 @@
         <v>100</v>
       </c>
       <c r="H94" s="18" t="s">
-        <v>466</v>
+        <v>665</v>
       </c>
       <c r="I94" s="15" t="s">
         <v>88</v>
@@ -7279,7 +7337,7 @@
         <v>3070301</v>
       </c>
       <c r="L94" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M94" s="15">
         <v>3570001</v>
@@ -7308,7 +7366,7 @@
         <v>100</v>
       </c>
       <c r="H95" s="18" t="s">
-        <v>467</v>
+        <v>666</v>
       </c>
       <c r="I95" s="15" t="s">
         <v>88</v>
@@ -7320,7 +7378,7 @@
         <v>3070301</v>
       </c>
       <c r="L95" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M95" s="15">
         <v>3570001</v>
@@ -7349,7 +7407,7 @@
         <v>100</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>468</v>
+        <v>667</v>
       </c>
       <c r="I96" s="15" t="s">
         <v>88</v>
@@ -7361,7 +7419,7 @@
         <v>3070301</v>
       </c>
       <c r="L96" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M96" s="15">
         <v>3570001</v>
@@ -7390,7 +7448,7 @@
         <v>100</v>
       </c>
       <c r="H97" s="18" t="s">
-        <v>469</v>
+        <v>668</v>
       </c>
       <c r="I97" s="15" t="s">
         <v>88</v>
@@ -7402,7 +7460,7 @@
         <v>3070301</v>
       </c>
       <c r="L97" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M97" s="15">
         <v>3570001</v>
@@ -7431,7 +7489,7 @@
         <v>100</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>470</v>
+        <v>669</v>
       </c>
       <c r="I98" s="15" t="s">
         <v>149</v>
@@ -7443,7 +7501,7 @@
         <v>3080001</v>
       </c>
       <c r="L98" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M98" s="15">
         <v>3580001</v>
@@ -7472,7 +7530,7 @@
         <v>100</v>
       </c>
       <c r="H99" s="18" t="s">
-        <v>471</v>
+        <v>670</v>
       </c>
       <c r="I99" s="15" t="s">
         <v>149</v>
@@ -7484,7 +7542,7 @@
         <v>3080001</v>
       </c>
       <c r="L99" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M99" s="15">
         <v>3580001</v>
@@ -7513,7 +7571,7 @@
         <v>100</v>
       </c>
       <c r="H100" s="18" t="s">
-        <v>472</v>
+        <v>671</v>
       </c>
       <c r="I100" s="15" t="s">
         <v>149</v>
@@ -7525,7 +7583,7 @@
         <v>3080001</v>
       </c>
       <c r="L100" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M100" s="15">
         <v>3580001</v>
@@ -7554,7 +7612,7 @@
         <v>100</v>
       </c>
       <c r="H101" s="18" t="s">
-        <v>473</v>
+        <v>672</v>
       </c>
       <c r="I101" s="15" t="s">
         <v>149</v>
@@ -7566,7 +7624,7 @@
         <v>3080001</v>
       </c>
       <c r="L101" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M101" s="15">
         <v>3580001</v>
@@ -7595,7 +7653,7 @@
         <v>100</v>
       </c>
       <c r="H102" s="18" t="s">
-        <v>474</v>
+        <v>673</v>
       </c>
       <c r="I102" s="15" t="s">
         <v>149</v>
@@ -7607,7 +7665,7 @@
         <v>3080001</v>
       </c>
       <c r="L102" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M102" s="15">
         <v>3580001</v>
@@ -7636,7 +7694,7 @@
         <v>100</v>
       </c>
       <c r="H103" s="18" t="s">
-        <v>475</v>
+        <v>674</v>
       </c>
       <c r="I103" s="15" t="s">
         <v>93</v>
@@ -7648,7 +7706,7 @@
         <v>3080102</v>
       </c>
       <c r="L103" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M103" s="15">
         <v>3580001</v>
@@ -7677,7 +7735,7 @@
         <v>100</v>
       </c>
       <c r="H104" s="18" t="s">
-        <v>476</v>
+        <v>675</v>
       </c>
       <c r="I104" s="15" t="s">
         <v>93</v>
@@ -7689,7 +7747,7 @@
         <v>3080102</v>
       </c>
       <c r="L104" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M104" s="15">
         <v>3580001</v>
@@ -7718,7 +7776,7 @@
         <v>100</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>477</v>
+        <v>676</v>
       </c>
       <c r="I105" s="15" t="s">
         <v>93</v>
@@ -7730,7 +7788,7 @@
         <v>3080102</v>
       </c>
       <c r="L105" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M105" s="15">
         <v>3580001</v>
@@ -7759,7 +7817,7 @@
         <v>100</v>
       </c>
       <c r="H106" s="18" t="s">
-        <v>478</v>
+        <v>677</v>
       </c>
       <c r="I106" s="15" t="s">
         <v>93</v>
@@ -7771,7 +7829,7 @@
         <v>3080102</v>
       </c>
       <c r="L106" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M106" s="15">
         <v>3580001</v>
@@ -7800,7 +7858,7 @@
         <v>100</v>
       </c>
       <c r="H107" s="18" t="s">
-        <v>479</v>
+        <v>678</v>
       </c>
       <c r="I107" s="15" t="s">
         <v>93</v>
@@ -7812,7 +7870,7 @@
         <v>3080102</v>
       </c>
       <c r="L107" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M107" s="15">
         <v>3580001</v>
@@ -7841,7 +7899,7 @@
         <v>100</v>
       </c>
       <c r="H108" s="18" t="s">
-        <v>480</v>
+        <v>679</v>
       </c>
       <c r="I108" s="15" t="s">
         <v>94</v>
@@ -7853,7 +7911,7 @@
         <v>3080301</v>
       </c>
       <c r="L108" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M108" s="15">
         <v>3580001</v>
@@ -7882,7 +7940,7 @@
         <v>100</v>
       </c>
       <c r="H109" s="18" t="s">
-        <v>481</v>
+        <v>680</v>
       </c>
       <c r="I109" s="15" t="s">
         <v>94</v>
@@ -7894,7 +7952,7 @@
         <v>3080301</v>
       </c>
       <c r="L109" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M109" s="15">
         <v>3580001</v>
@@ -7923,7 +7981,7 @@
         <v>100</v>
       </c>
       <c r="H110" s="18" t="s">
-        <v>482</v>
+        <v>681</v>
       </c>
       <c r="I110" s="15" t="s">
         <v>94</v>
@@ -7935,7 +7993,7 @@
         <v>3080301</v>
       </c>
       <c r="L110" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M110" s="15">
         <v>3580001</v>
@@ -7964,7 +8022,7 @@
         <v>100</v>
       </c>
       <c r="H111" s="18" t="s">
-        <v>483</v>
+        <v>682</v>
       </c>
       <c r="I111" s="15" t="s">
         <v>94</v>
@@ -7976,7 +8034,7 @@
         <v>3080301</v>
       </c>
       <c r="L111" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M111" s="15">
         <v>3580001</v>
@@ -8005,7 +8063,7 @@
         <v>100</v>
       </c>
       <c r="H112" s="18" t="s">
-        <v>484</v>
+        <v>683</v>
       </c>
       <c r="I112" s="15" t="s">
         <v>94</v>
@@ -8017,7 +8075,7 @@
         <v>3080301</v>
       </c>
       <c r="L112" s="15" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M112" s="15">
         <v>3580001</v>
@@ -8037,7 +8095,7 @@
         <v>1</v>
       </c>
       <c r="E113" s="21" t="s">
-        <v>577</v>
+        <v>485</v>
       </c>
       <c r="F113" s="20">
         <v>1</v>
@@ -8046,19 +8104,19 @@
         <v>500</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>747</v>
+        <v>684</v>
       </c>
       <c r="I113" s="20" t="s">
         <v>392</v>
       </c>
       <c r="J113" s="20" t="s">
-        <v>654</v>
+        <v>531</v>
       </c>
       <c r="K113" s="20">
         <v>3050001</v>
       </c>
       <c r="L113" s="20" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M113" s="20">
         <v>3550001</v>
@@ -8087,19 +8145,19 @@
         <v>500</v>
       </c>
       <c r="H114" s="20" t="s">
-        <v>765</v>
+        <v>685</v>
       </c>
       <c r="I114" s="20" t="s">
         <v>393</v>
       </c>
       <c r="J114" s="20" t="s">
-        <v>748</v>
+        <v>584</v>
       </c>
       <c r="K114" s="20">
         <v>3050301</v>
       </c>
       <c r="L114" s="20" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M114" s="20">
         <v>3550002</v>
@@ -8128,17 +8186,17 @@
         <v>500</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>655</v>
+        <v>770</v>
       </c>
       <c r="I115" s="20" t="s">
-        <v>656</v>
+        <v>532</v>
       </c>
       <c r="J115" s="20" t="s">
-        <v>767</v>
+        <v>590</v>
       </c>
       <c r="K115" s="20"/>
       <c r="L115" s="20" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M115" s="20">
         <v>3550003</v>
@@ -8167,7 +8225,7 @@
         <v>500</v>
       </c>
       <c r="H116" s="20" t="s">
-        <v>766</v>
+        <v>777</v>
       </c>
       <c r="I116" s="20" t="s">
         <v>395</v>
@@ -8179,7 +8237,7 @@
         <v>3050301</v>
       </c>
       <c r="L116" s="20" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M116" s="20">
         <v>3550002</v>
@@ -8208,19 +8266,19 @@
         <v>500</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>764</v>
+        <v>778</v>
       </c>
       <c r="I117" s="20" t="s">
         <v>396</v>
       </c>
       <c r="J117" s="20" t="s">
-        <v>749</v>
+        <v>585</v>
       </c>
       <c r="K117" s="20">
         <v>3550501</v>
       </c>
       <c r="L117" s="20" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M117" s="20">
         <v>3550003</v>
@@ -8249,7 +8307,7 @@
         <v>500</v>
       </c>
       <c r="H118" s="20" t="s">
-        <v>763</v>
+        <v>779</v>
       </c>
       <c r="I118" s="20" t="s">
         <v>397</v>
@@ -8261,7 +8319,7 @@
         <v>3050301</v>
       </c>
       <c r="L118" s="20" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M118" s="20">
         <v>3550002</v>
@@ -8290,19 +8348,19 @@
         <v>500</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>764</v>
+        <v>780</v>
       </c>
       <c r="I119" s="20" t="s">
         <v>398</v>
       </c>
       <c r="J119" s="20" t="s">
-        <v>749</v>
+        <v>585</v>
       </c>
       <c r="K119" s="20">
         <v>3550501</v>
       </c>
       <c r="L119" s="20" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M119" s="20">
         <v>3550003</v>
@@ -8331,7 +8389,7 @@
         <v>500</v>
       </c>
       <c r="H120" s="20" t="s">
-        <v>750</v>
+        <v>781</v>
       </c>
       <c r="I120" s="20" t="s">
         <v>399</v>
@@ -8343,7 +8401,7 @@
         <v>3050301</v>
       </c>
       <c r="L120" s="20" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M120" s="20">
         <v>3550002</v>
@@ -8363,7 +8421,7 @@
         <v>1</v>
       </c>
       <c r="E121" s="23" t="s">
-        <v>577</v>
+        <v>485</v>
       </c>
       <c r="F121" s="22">
         <v>1</v>
@@ -8372,19 +8430,19 @@
         <v>500</v>
       </c>
       <c r="H121" s="22" t="s">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="I121" s="22" t="s">
-        <v>490</v>
+        <v>405</v>
       </c>
       <c r="J121" s="22" t="s">
-        <v>665</v>
+        <v>538</v>
       </c>
       <c r="K121" s="22">
         <v>3060001</v>
       </c>
       <c r="L121" s="22" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M121" s="22">
         <v>3560001</v>
@@ -8413,19 +8471,19 @@
         <v>500</v>
       </c>
       <c r="H122" s="22" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
       <c r="I122" s="22" t="s">
-        <v>488</v>
+        <v>403</v>
       </c>
       <c r="J122" s="22" t="s">
-        <v>723</v>
+        <v>574</v>
       </c>
       <c r="K122" s="22">
         <v>3060102</v>
       </c>
       <c r="L122" s="22" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M122" s="22">
         <v>3560002</v>
@@ -8454,17 +8512,17 @@
         <v>500</v>
       </c>
       <c r="H123" s="22" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="I123" s="22" t="s">
-        <v>501</v>
+        <v>416</v>
       </c>
       <c r="J123" s="22" t="s">
-        <v>724</v>
+        <v>575</v>
       </c>
       <c r="K123" s="22"/>
       <c r="L123" s="22" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M123" s="22">
         <v>3560003</v>
@@ -8493,19 +8551,19 @@
         <v>500</v>
       </c>
       <c r="H124" s="22" t="s">
-        <v>652</v>
+        <v>688</v>
       </c>
       <c r="I124" s="22" t="s">
-        <v>489</v>
+        <v>404</v>
       </c>
       <c r="J124" s="22" t="s">
-        <v>728</v>
+        <v>579</v>
       </c>
       <c r="K124" s="24" t="s">
-        <v>565</v>
+        <v>476</v>
       </c>
       <c r="L124" s="22" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M124" s="24">
         <v>3560002</v>
@@ -8534,17 +8592,17 @@
         <v>500</v>
       </c>
       <c r="H125" s="22" t="s">
-        <v>734</v>
+        <v>689</v>
       </c>
       <c r="I125" s="22" t="s">
-        <v>485</v>
+        <v>400</v>
       </c>
       <c r="J125" s="22" t="s">
-        <v>722</v>
+        <v>573</v>
       </c>
       <c r="K125" s="22"/>
       <c r="L125" s="22" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M125" s="22">
         <v>3560003</v>
@@ -8573,19 +8631,19 @@
         <v>500</v>
       </c>
       <c r="H126" s="22" t="s">
-        <v>735</v>
+        <v>690</v>
       </c>
       <c r="I126" s="22" t="s">
-        <v>491</v>
+        <v>406</v>
       </c>
       <c r="J126" s="22" t="s">
-        <v>671</v>
+        <v>539</v>
       </c>
       <c r="K126" s="22">
         <v>3060102</v>
       </c>
       <c r="L126" s="22" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M126" s="22">
         <v>3560002</v>
@@ -8614,19 +8672,19 @@
         <v>500</v>
       </c>
       <c r="H127" s="22" t="s">
-        <v>736</v>
+        <v>691</v>
       </c>
       <c r="I127" s="22" t="s">
-        <v>486</v>
+        <v>401</v>
       </c>
       <c r="J127" s="22" t="s">
-        <v>673</v>
+        <v>540</v>
       </c>
       <c r="K127" s="22">
         <v>3060102</v>
       </c>
       <c r="L127" s="22" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M127" s="22">
         <v>3560003</v>
@@ -8655,17 +8713,17 @@
         <v>500</v>
       </c>
       <c r="H128" s="22" t="s">
-        <v>737</v>
+        <v>692</v>
       </c>
       <c r="I128" s="22" t="s">
-        <v>492</v>
+        <v>407</v>
       </c>
       <c r="J128" s="22" t="s">
-        <v>515</v>
+        <v>427</v>
       </c>
       <c r="K128" s="25"/>
       <c r="L128" s="22" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M128" s="22">
         <v>3560004</v>
@@ -8685,7 +8743,7 @@
         <v>1</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>588</v>
+        <v>496</v>
       </c>
       <c r="F129" s="26">
         <v>1</v>
@@ -8694,19 +8752,19 @@
         <v>500</v>
       </c>
       <c r="H129" s="26" t="s">
-        <v>455</v>
+        <v>693</v>
       </c>
       <c r="I129" s="26" t="s">
-        <v>487</v>
+        <v>402</v>
       </c>
       <c r="J129" s="26" t="s">
-        <v>516</v>
+        <v>428</v>
       </c>
       <c r="K129" s="26">
         <v>3070001</v>
       </c>
       <c r="L129" s="26" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M129" s="26">
         <v>3570001</v>
@@ -8735,19 +8793,19 @@
         <v>500</v>
       </c>
       <c r="H130" s="26" t="s">
-        <v>463</v>
+        <v>662</v>
       </c>
       <c r="I130" s="26" t="s">
-        <v>493</v>
+        <v>408</v>
       </c>
       <c r="J130" s="26" t="s">
-        <v>578</v>
+        <v>486</v>
       </c>
       <c r="K130" s="28" t="s">
-        <v>566</v>
+        <v>477</v>
       </c>
       <c r="L130" s="26" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M130" s="26">
         <v>3570002</v>
@@ -8776,17 +8834,17 @@
         <v>500</v>
       </c>
       <c r="H131" s="26" t="s">
-        <v>590</v>
+        <v>694</v>
       </c>
       <c r="I131" s="26" t="s">
-        <v>496</v>
+        <v>411</v>
       </c>
       <c r="J131" s="26" t="s">
-        <v>517</v>
+        <v>429</v>
       </c>
       <c r="K131" s="26"/>
       <c r="L131" s="26" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M131" s="26">
         <v>3570003</v>
@@ -8815,19 +8873,19 @@
         <v>500</v>
       </c>
       <c r="H132" s="26" t="s">
-        <v>463</v>
+        <v>695</v>
       </c>
       <c r="I132" s="26" t="s">
-        <v>494</v>
+        <v>409</v>
       </c>
       <c r="J132" s="26" t="s">
-        <v>518</v>
+        <v>430</v>
       </c>
       <c r="K132" s="28" t="s">
-        <v>566</v>
+        <v>477</v>
       </c>
       <c r="L132" s="26" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M132" s="26">
         <v>3570002</v>
@@ -8856,17 +8914,17 @@
         <v>500</v>
       </c>
       <c r="H133" s="26" t="s">
-        <v>591</v>
+        <v>696</v>
       </c>
       <c r="I133" s="26" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="J133" s="26" t="s">
-        <v>567</v>
+        <v>478</v>
       </c>
       <c r="K133" s="26"/>
       <c r="L133" s="26" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M133" s="26">
         <v>3570003</v>
@@ -8895,19 +8953,19 @@
         <v>500</v>
       </c>
       <c r="H134" s="26" t="s">
-        <v>592</v>
+        <v>697</v>
       </c>
       <c r="I134" s="26" t="s">
-        <v>607</v>
+        <v>504</v>
       </c>
       <c r="J134" s="26" t="s">
-        <v>519</v>
+        <v>431</v>
       </c>
       <c r="K134" s="26">
         <v>3070102</v>
       </c>
       <c r="L134" s="26" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M134" s="26">
         <v>3570002</v>
@@ -8936,19 +8994,19 @@
         <v>500</v>
       </c>
       <c r="H135" s="26" t="s">
-        <v>593</v>
+        <v>698</v>
       </c>
       <c r="I135" s="26" t="s">
-        <v>497</v>
+        <v>412</v>
       </c>
       <c r="J135" s="26" t="s">
-        <v>520</v>
+        <v>432</v>
       </c>
       <c r="K135" s="26">
         <v>3070102</v>
       </c>
       <c r="L135" s="26" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M135" s="26">
         <v>3570003</v>
@@ -8977,17 +9035,17 @@
         <v>500</v>
       </c>
       <c r="H136" s="26" t="s">
-        <v>594</v>
+        <v>699</v>
       </c>
       <c r="I136" s="26" t="s">
-        <v>498</v>
+        <v>413</v>
       </c>
       <c r="J136" s="26" t="s">
-        <v>521</v>
+        <v>433</v>
       </c>
       <c r="K136" s="29"/>
       <c r="L136" s="26" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M136" s="26">
         <v>3570001</v>
@@ -9007,7 +9065,7 @@
         <v>1</v>
       </c>
       <c r="E137" s="31" t="s">
-        <v>588</v>
+        <v>496</v>
       </c>
       <c r="F137" s="30">
         <v>1</v>
@@ -9016,19 +9074,19 @@
         <v>500</v>
       </c>
       <c r="H137" s="30" t="s">
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="I137" s="30" t="s">
-        <v>499</v>
+        <v>414</v>
       </c>
       <c r="J137" s="30" t="s">
-        <v>579</v>
+        <v>487</v>
       </c>
       <c r="K137" s="30">
         <v>3080001</v>
       </c>
       <c r="L137" s="30" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M137" s="30">
         <v>3580001</v>
@@ -9057,19 +9115,19 @@
         <v>500</v>
       </c>
       <c r="H138" s="30" t="s">
-        <v>478</v>
+        <v>677</v>
       </c>
       <c r="I138" s="30" t="s">
-        <v>500</v>
+        <v>415</v>
       </c>
       <c r="J138" s="30" t="s">
-        <v>522</v>
+        <v>434</v>
       </c>
       <c r="K138" s="32" t="s">
-        <v>556</v>
+        <v>467</v>
       </c>
       <c r="L138" s="30" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M138" s="30">
         <v>3580002</v>
@@ -9098,19 +9156,19 @@
         <v>500</v>
       </c>
       <c r="H139" s="30" t="s">
-        <v>478</v>
+        <v>701</v>
       </c>
       <c r="I139" s="30" t="s">
-        <v>504</v>
+        <v>419</v>
       </c>
       <c r="J139" s="30" t="s">
-        <v>523</v>
+        <v>435</v>
       </c>
       <c r="K139" s="30">
         <v>3080102</v>
       </c>
       <c r="L139" s="30" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M139" s="30">
         <v>3580003</v>
@@ -9139,19 +9197,19 @@
         <v>500</v>
       </c>
       <c r="H140" s="30" t="s">
-        <v>478</v>
+        <v>702</v>
       </c>
       <c r="I140" s="30" t="s">
-        <v>502</v>
+        <v>417</v>
       </c>
       <c r="J140" s="30" t="s">
-        <v>524</v>
+        <v>436</v>
       </c>
       <c r="K140" s="30">
         <v>3080102</v>
       </c>
       <c r="L140" s="30" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M140" s="30">
         <v>3580002</v>
@@ -9180,19 +9238,19 @@
         <v>500</v>
       </c>
       <c r="H141" s="30" t="s">
-        <v>595</v>
+        <v>703</v>
       </c>
       <c r="I141" s="30" t="s">
-        <v>505</v>
+        <v>420</v>
       </c>
       <c r="J141" s="30" t="s">
-        <v>525</v>
+        <v>437</v>
       </c>
       <c r="K141" s="30">
         <v>3080102</v>
       </c>
       <c r="L141" s="30" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M141" s="30">
         <v>3580003</v>
@@ -9221,19 +9279,19 @@
         <v>500</v>
       </c>
       <c r="H142" s="30" t="s">
-        <v>596</v>
+        <v>704</v>
       </c>
       <c r="I142" s="30" t="s">
-        <v>506</v>
+        <v>421</v>
       </c>
       <c r="J142" s="30" t="s">
-        <v>580</v>
+        <v>488</v>
       </c>
       <c r="K142" s="30">
         <v>3080102</v>
       </c>
       <c r="L142" s="30" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M142" s="30">
         <v>3580002</v>
@@ -9262,19 +9320,19 @@
         <v>500</v>
       </c>
       <c r="H143" s="30" t="s">
-        <v>597</v>
+        <v>705</v>
       </c>
       <c r="I143" s="30" t="s">
-        <v>507</v>
+        <v>422</v>
       </c>
       <c r="J143" s="30" t="s">
-        <v>526</v>
+        <v>438</v>
       </c>
       <c r="K143" s="30">
         <v>3080102</v>
       </c>
       <c r="L143" s="30" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M143" s="30">
         <v>3580003</v>
@@ -9303,19 +9361,19 @@
         <v>500</v>
       </c>
       <c r="H144" s="30" t="s">
-        <v>598</v>
+        <v>706</v>
       </c>
       <c r="I144" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="J144" s="30" t="s">
+        <v>439</v>
+      </c>
+      <c r="K144" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="L144" s="30" t="s">
         <v>503</v>
-      </c>
-      <c r="J144" s="30" t="s">
-        <v>527</v>
-      </c>
-      <c r="K144" s="33" t="s">
-        <v>557</v>
-      </c>
-      <c r="L144" s="30" t="s">
-        <v>606</v>
       </c>
       <c r="M144" s="32">
         <v>3580001</v>
@@ -9344,19 +9402,19 @@
         <v>500</v>
       </c>
       <c r="H145" s="36" t="s">
-        <v>568</v>
+        <v>707</v>
       </c>
       <c r="I145" s="34" t="s">
-        <v>528</v>
+        <v>440</v>
       </c>
       <c r="J145" s="34" t="s">
-        <v>529</v>
+        <v>441</v>
       </c>
       <c r="K145" s="36" t="s">
-        <v>558</v>
+        <v>469</v>
       </c>
       <c r="L145" s="34" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M145" s="36">
         <v>3590001</v>
@@ -9385,19 +9443,19 @@
         <v>500</v>
       </c>
       <c r="H146" s="36" t="s">
-        <v>573</v>
+        <v>708</v>
       </c>
       <c r="I146" s="34" t="s">
-        <v>509</v>
+        <v>424</v>
       </c>
       <c r="J146" s="34" t="s">
-        <v>530</v>
+        <v>442</v>
       </c>
       <c r="K146" s="34">
         <v>3041102</v>
       </c>
       <c r="L146" s="34" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M146" s="36">
         <v>3590002</v>
@@ -9426,19 +9484,19 @@
         <v>500</v>
       </c>
       <c r="H147" s="36" t="s">
-        <v>573</v>
+        <v>709</v>
       </c>
       <c r="I147" s="34" t="s">
-        <v>510</v>
+        <v>425</v>
       </c>
       <c r="J147" s="34" t="s">
-        <v>531</v>
+        <v>443</v>
       </c>
       <c r="K147" s="34">
         <v>3041102</v>
       </c>
       <c r="L147" s="34" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M147" s="36">
         <v>3590002</v>
@@ -9467,17 +9525,17 @@
         <v>500</v>
       </c>
       <c r="H148" s="36" t="s">
-        <v>512</v>
+        <v>710</v>
       </c>
       <c r="I148" s="34" t="s">
-        <v>508</v>
+        <v>423</v>
       </c>
       <c r="J148" s="34" t="s">
-        <v>532</v>
+        <v>444</v>
       </c>
       <c r="K148" s="34"/>
       <c r="L148" s="34" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M148" s="36">
         <v>3590003</v>
@@ -9506,19 +9564,19 @@
         <v>500</v>
       </c>
       <c r="H149" s="36" t="s">
-        <v>573</v>
+        <v>711</v>
       </c>
       <c r="I149" s="34" t="s">
-        <v>533</v>
+        <v>445</v>
       </c>
       <c r="J149" s="34" t="s">
-        <v>581</v>
+        <v>489</v>
       </c>
       <c r="K149" s="34">
         <v>3041102</v>
       </c>
       <c r="L149" s="34" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M149" s="36">
         <v>3590004</v>
@@ -9547,17 +9605,17 @@
         <v>500</v>
       </c>
       <c r="H150" s="36" t="s">
-        <v>512</v>
+        <v>712</v>
       </c>
       <c r="I150" s="34" t="s">
-        <v>511</v>
+        <v>426</v>
       </c>
       <c r="J150" s="34" t="s">
-        <v>534</v>
+        <v>446</v>
       </c>
       <c r="K150" s="34"/>
       <c r="L150" s="34" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M150" s="36">
         <v>3590005</v>
@@ -9586,10 +9644,10 @@
         <v>500</v>
       </c>
       <c r="H151" s="39" t="s">
-        <v>648</v>
+        <v>713</v>
       </c>
       <c r="I151" s="37" t="s">
-        <v>535</v>
+        <v>447</v>
       </c>
       <c r="J151" s="37" t="s">
         <v>29</v>
@@ -9598,7 +9656,7 @@
         <v>3040102</v>
       </c>
       <c r="L151" s="37" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M151" s="37">
         <v>3600001</v>
@@ -9627,19 +9685,19 @@
         <v>500</v>
       </c>
       <c r="H152" s="39" t="s">
-        <v>755</v>
+        <v>714</v>
       </c>
       <c r="I152" s="37" t="s">
-        <v>536</v>
+        <v>448</v>
       </c>
       <c r="J152" s="37" t="s">
-        <v>753</v>
+        <v>588</v>
       </c>
       <c r="K152" s="39" t="s">
-        <v>751</v>
+        <v>586</v>
       </c>
       <c r="L152" s="37" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M152" s="37">
         <v>3600001</v>
@@ -9668,19 +9726,19 @@
         <v>500</v>
       </c>
       <c r="H153" s="39" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="I153" s="37" t="s">
-        <v>537</v>
+        <v>449</v>
       </c>
       <c r="J153" s="37" t="s">
-        <v>752</v>
+        <v>587</v>
       </c>
       <c r="K153" s="39" t="s">
-        <v>754</v>
+        <v>589</v>
       </c>
       <c r="L153" s="37" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M153" s="37">
         <v>3600002</v>
@@ -9709,17 +9767,17 @@
         <v>500</v>
       </c>
       <c r="H154" s="39" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="I154" s="37" t="s">
-        <v>538</v>
+        <v>450</v>
       </c>
       <c r="J154" s="37" t="s">
-        <v>725</v>
+        <v>576</v>
       </c>
       <c r="K154" s="37"/>
       <c r="L154" s="37" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M154" s="37">
         <v>3600003</v>
@@ -9748,17 +9806,17 @@
         <v>500</v>
       </c>
       <c r="H155" s="39" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="I155" s="37" t="s">
-        <v>539</v>
+        <v>451</v>
       </c>
       <c r="J155" s="37" t="s">
-        <v>726</v>
+        <v>577</v>
       </c>
       <c r="K155" s="37"/>
       <c r="L155" s="37" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M155" s="37">
         <v>3600002</v>
@@ -9787,17 +9845,19 @@
         <v>500</v>
       </c>
       <c r="H156" s="39" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="I156" s="37" t="s">
-        <v>540</v>
+        <v>591</v>
       </c>
       <c r="J156" s="37" t="s">
-        <v>541</v>
-      </c>
-      <c r="K156" s="37"/>
+        <v>588</v>
+      </c>
+      <c r="K156" s="39" t="s">
+        <v>586</v>
+      </c>
       <c r="L156" s="37" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M156" s="37">
         <v>3600002</v>
@@ -9826,17 +9886,17 @@
         <v>500</v>
       </c>
       <c r="H157" s="39" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="I157" s="37" t="s">
-        <v>542</v>
+        <v>453</v>
       </c>
       <c r="J157" s="37" t="s">
-        <v>543</v>
+        <v>454</v>
       </c>
       <c r="K157" s="37"/>
       <c r="L157" s="37" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M157" s="37">
         <v>3600003</v>
@@ -9865,17 +9925,17 @@
         <v>500</v>
       </c>
       <c r="H158" s="39" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="I158" s="37" t="s">
-        <v>544</v>
+        <v>455</v>
       </c>
       <c r="J158" s="37" t="s">
-        <v>545</v>
+        <v>456</v>
       </c>
       <c r="K158" s="37"/>
       <c r="L158" s="37" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M158" s="37">
         <v>3600004</v>
@@ -9904,10 +9964,10 @@
         <v>500</v>
       </c>
       <c r="H159" s="43" t="s">
-        <v>415</v>
+        <v>715</v>
       </c>
       <c r="I159" s="41" t="s">
-        <v>559</v>
+        <v>470</v>
       </c>
       <c r="J159" s="41" t="s">
         <v>38</v>
@@ -9916,7 +9976,7 @@
         <v>3041001</v>
       </c>
       <c r="L159" s="41" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M159" s="41">
         <v>3610001</v>
@@ -9945,17 +10005,17 @@
         <v>500</v>
       </c>
       <c r="H160" s="43" t="s">
-        <v>415</v>
+        <v>716</v>
       </c>
       <c r="I160" s="41" t="s">
-        <v>546</v>
+        <v>457</v>
       </c>
       <c r="J160" s="41" t="s">
-        <v>547</v>
+        <v>458</v>
       </c>
       <c r="K160" s="41"/>
       <c r="L160" s="41" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M160" s="41">
         <v>3610002</v>
@@ -9975,7 +10035,7 @@
         <v>2</v>
       </c>
       <c r="E161" s="42" t="s">
-        <v>569</v>
+        <v>479</v>
       </c>
       <c r="F161" s="41">
         <v>1</v>
@@ -9984,17 +10044,17 @@
         <v>500</v>
       </c>
       <c r="H161" s="43" t="s">
-        <v>416</v>
+        <v>717</v>
       </c>
       <c r="I161" s="41" t="s">
-        <v>548</v>
+        <v>459</v>
       </c>
       <c r="J161" s="41" t="s">
-        <v>560</v>
+        <v>471</v>
       </c>
       <c r="K161" s="41"/>
       <c r="L161" s="41" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M161" s="41">
         <v>3610002</v>
@@ -10023,17 +10083,17 @@
         <v>500</v>
       </c>
       <c r="H162" s="43" t="s">
-        <v>416</v>
+        <v>718</v>
       </c>
       <c r="I162" s="41" t="s">
-        <v>549</v>
+        <v>460</v>
       </c>
       <c r="J162" s="41" t="s">
-        <v>550</v>
+        <v>461</v>
       </c>
       <c r="K162" s="41"/>
       <c r="L162" s="41" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M162" s="41">
         <v>3610003</v>
@@ -10053,7 +10113,7 @@
         <v>3</v>
       </c>
       <c r="E163" s="42" t="s">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="F163" s="41">
         <v>1</v>
@@ -10062,17 +10122,17 @@
         <v>500</v>
       </c>
       <c r="H163" s="43" t="s">
-        <v>417</v>
+        <v>719</v>
       </c>
       <c r="I163" s="41" t="s">
-        <v>551</v>
+        <v>462</v>
       </c>
       <c r="J163" s="41" t="s">
-        <v>561</v>
+        <v>472</v>
       </c>
       <c r="K163" s="41"/>
       <c r="L163" s="41" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M163" s="41">
         <v>3610003</v>
@@ -10092,7 +10152,7 @@
         <v>4</v>
       </c>
       <c r="E164" s="44" t="s">
-        <v>571</v>
+        <v>481</v>
       </c>
       <c r="F164" s="41">
         <v>1</v>
@@ -10101,17 +10161,17 @@
         <v>500</v>
       </c>
       <c r="H164" s="43" t="s">
-        <v>417</v>
+        <v>720</v>
       </c>
       <c r="I164" s="41" t="s">
-        <v>552</v>
+        <v>463</v>
       </c>
       <c r="J164" s="41" t="s">
-        <v>553</v>
+        <v>464</v>
       </c>
       <c r="K164" s="41"/>
       <c r="L164" s="41" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M164" s="41">
         <v>3610002</v>
@@ -10140,19 +10200,19 @@
         <v>500</v>
       </c>
       <c r="H165" s="43" t="s">
-        <v>418</v>
+        <v>721</v>
       </c>
       <c r="I165" s="41" t="s">
-        <v>554</v>
+        <v>465</v>
       </c>
       <c r="J165" s="41" t="s">
-        <v>562</v>
+        <v>473</v>
       </c>
       <c r="K165" s="43" t="s">
-        <v>563</v>
+        <v>474</v>
       </c>
       <c r="L165" s="41" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M165" s="41">
         <v>3610004</v>
@@ -10181,17 +10241,17 @@
         <v>500</v>
       </c>
       <c r="H166" s="43" t="s">
-        <v>419</v>
+        <v>722</v>
       </c>
       <c r="I166" s="41" t="s">
-        <v>555</v>
+        <v>466</v>
       </c>
       <c r="J166" s="41" t="s">
-        <v>564</v>
+        <v>475</v>
       </c>
       <c r="K166" s="41"/>
       <c r="L166" s="41" t="s">
-        <v>606</v>
+        <v>503</v>
       </c>
       <c r="M166" s="41">
         <v>3610004</v>
@@ -10211,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="E167" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F167" s="45">
         <v>1</v>
@@ -10220,17 +10280,17 @@
         <v>1</v>
       </c>
       <c r="H167" s="45" t="s">
-        <v>622</v>
+        <v>723</v>
       </c>
       <c r="I167" s="45" t="s">
-        <v>609</v>
+        <v>506</v>
       </c>
       <c r="J167" s="45" t="s">
-        <v>634</v>
+        <v>519</v>
       </c>
       <c r="K167" s="45"/>
       <c r="L167" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M167" s="45">
         <v>3610004</v>
@@ -10250,7 +10310,7 @@
         <v>1</v>
       </c>
       <c r="E168" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F168" s="45">
         <v>1</v>
@@ -10259,17 +10319,17 @@
         <v>1</v>
       </c>
       <c r="H168" s="45" t="s">
-        <v>623</v>
+        <v>724</v>
       </c>
       <c r="I168" s="45" t="s">
-        <v>610</v>
+        <v>507</v>
       </c>
       <c r="J168" s="45" t="s">
-        <v>635</v>
+        <v>520</v>
       </c>
       <c r="K168" s="45"/>
       <c r="L168" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M168" s="45">
         <v>3610004</v>
@@ -10289,7 +10349,7 @@
         <v>1</v>
       </c>
       <c r="E169" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F169" s="45">
         <v>1</v>
@@ -10298,17 +10358,17 @@
         <v>1</v>
       </c>
       <c r="H169" s="45" t="s">
-        <v>624</v>
+        <v>725</v>
       </c>
       <c r="I169" s="45" t="s">
-        <v>611</v>
+        <v>508</v>
       </c>
       <c r="J169" s="45" t="s">
-        <v>636</v>
+        <v>521</v>
       </c>
       <c r="K169" s="45"/>
       <c r="L169" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M169" s="45">
         <v>3610004</v>
@@ -10328,7 +10388,7 @@
         <v>1</v>
       </c>
       <c r="E170" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F170" s="45">
         <v>1</v>
@@ -10337,17 +10397,17 @@
         <v>1</v>
       </c>
       <c r="H170" s="45" t="s">
-        <v>625</v>
+        <v>726</v>
       </c>
       <c r="I170" s="45" t="s">
-        <v>612</v>
+        <v>509</v>
       </c>
       <c r="J170" s="45" t="s">
-        <v>637</v>
+        <v>522</v>
       </c>
       <c r="K170" s="45"/>
       <c r="L170" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M170" s="45">
         <v>3610004</v>
@@ -10367,7 +10427,7 @@
         <v>1</v>
       </c>
       <c r="E171" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F171" s="45">
         <v>1</v>
@@ -10376,17 +10436,17 @@
         <v>1</v>
       </c>
       <c r="H171" s="45" t="s">
-        <v>626</v>
+        <v>727</v>
       </c>
       <c r="I171" s="45" t="s">
-        <v>613</v>
+        <v>510</v>
       </c>
       <c r="J171" s="45" t="s">
-        <v>638</v>
+        <v>523</v>
       </c>
       <c r="K171" s="45"/>
       <c r="L171" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M171" s="45">
         <v>3610004</v>
@@ -10406,7 +10466,7 @@
         <v>1</v>
       </c>
       <c r="E172" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F172" s="45">
         <v>1</v>
@@ -10415,17 +10475,17 @@
         <v>1</v>
       </c>
       <c r="H172" s="45" t="s">
-        <v>627</v>
+        <v>728</v>
       </c>
       <c r="I172" s="45" t="s">
-        <v>614</v>
+        <v>511</v>
       </c>
       <c r="J172" s="45" t="s">
-        <v>639</v>
+        <v>524</v>
       </c>
       <c r="K172" s="45"/>
       <c r="L172" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M172" s="45">
         <v>3610004</v>
@@ -10445,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="E173" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F173" s="45">
         <v>1</v>
@@ -10454,17 +10514,17 @@
         <v>1</v>
       </c>
       <c r="H173" s="45" t="s">
-        <v>628</v>
+        <v>729</v>
       </c>
       <c r="I173" s="45" t="s">
-        <v>615</v>
+        <v>512</v>
       </c>
       <c r="J173" s="45" t="s">
-        <v>640</v>
+        <v>525</v>
       </c>
       <c r="K173" s="45"/>
       <c r="L173" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M173" s="45">
         <v>3610004</v>
@@ -10484,7 +10544,7 @@
         <v>1</v>
       </c>
       <c r="E174" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F174" s="45">
         <v>1</v>
@@ -10493,17 +10553,17 @@
         <v>1</v>
       </c>
       <c r="H174" s="45" t="s">
-        <v>629</v>
+        <v>730</v>
       </c>
       <c r="I174" s="45" t="s">
-        <v>616</v>
+        <v>513</v>
       </c>
       <c r="J174" s="45" t="s">
-        <v>641</v>
+        <v>526</v>
       </c>
       <c r="K174" s="45"/>
       <c r="L174" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M174" s="45">
         <v>3610004</v>
@@ -10523,7 +10583,7 @@
         <v>1</v>
       </c>
       <c r="E175" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F175" s="45">
         <v>1</v>
@@ -10532,17 +10592,17 @@
         <v>1</v>
       </c>
       <c r="H175" s="45" t="s">
-        <v>630</v>
+        <v>731</v>
       </c>
       <c r="I175" s="45" t="s">
-        <v>617</v>
+        <v>514</v>
       </c>
       <c r="J175" s="45" t="s">
-        <v>653</v>
+        <v>530</v>
       </c>
       <c r="K175" s="45"/>
       <c r="L175" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M175" s="45">
         <v>3610004</v>
@@ -10562,7 +10622,7 @@
         <v>1</v>
       </c>
       <c r="E176" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F176" s="45">
         <v>1</v>
@@ -10571,17 +10631,17 @@
         <v>1</v>
       </c>
       <c r="H176" s="45" t="s">
-        <v>631</v>
+        <v>732</v>
       </c>
       <c r="I176" s="45" t="s">
-        <v>618</v>
+        <v>515</v>
       </c>
       <c r="J176" s="45" t="s">
-        <v>642</v>
+        <v>527</v>
       </c>
       <c r="K176" s="45"/>
       <c r="L176" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M176" s="45">
         <v>3610004</v>
@@ -10601,7 +10661,7 @@
         <v>1</v>
       </c>
       <c r="E177" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F177" s="45">
         <v>1</v>
@@ -10610,17 +10670,17 @@
         <v>1</v>
       </c>
       <c r="H177" s="45" t="s">
-        <v>632</v>
+        <v>733</v>
       </c>
       <c r="I177" s="45" t="s">
-        <v>619</v>
+        <v>516</v>
       </c>
       <c r="J177" s="45" t="s">
-        <v>643</v>
+        <v>528</v>
       </c>
       <c r="K177" s="45"/>
       <c r="L177" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M177" s="45">
         <v>3610004</v>
@@ -10640,7 +10700,7 @@
         <v>1</v>
       </c>
       <c r="E178" s="46" t="s">
-        <v>621</v>
+        <v>518</v>
       </c>
       <c r="F178" s="45">
         <v>1</v>
@@ -10649,17 +10709,17 @@
         <v>1</v>
       </c>
       <c r="H178" s="45" t="s">
-        <v>633</v>
+        <v>734</v>
       </c>
       <c r="I178" s="45" t="s">
-        <v>620</v>
+        <v>517</v>
       </c>
       <c r="J178" s="45" t="s">
-        <v>644</v>
+        <v>529</v>
       </c>
       <c r="K178" s="45"/>
       <c r="L178" s="45" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M178" s="45">
         <v>3610004</v>
@@ -10679,7 +10739,7 @@
         <v>1</v>
       </c>
       <c r="E179" s="21" t="s">
-        <v>727</v>
+        <v>578</v>
       </c>
       <c r="F179" s="20">
         <v>1</v>
@@ -10688,19 +10748,19 @@
         <v>500</v>
       </c>
       <c r="H179" s="20" t="s">
-        <v>740</v>
+        <v>684</v>
       </c>
       <c r="I179" s="20" t="s">
         <v>392</v>
       </c>
       <c r="J179" s="48" t="s">
-        <v>654</v>
+        <v>531</v>
       </c>
       <c r="K179" s="20">
         <v>3050001</v>
       </c>
       <c r="L179" s="20" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M179" s="20">
         <v>3550001</v>
@@ -10729,19 +10789,19 @@
         <v>500</v>
       </c>
       <c r="H180" s="20" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I180" s="20" t="s">
         <v>393</v>
       </c>
       <c r="J180" s="48" t="s">
-        <v>738</v>
+        <v>580</v>
       </c>
       <c r="K180" s="20">
         <v>3050301</v>
       </c>
       <c r="L180" s="20" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M180" s="20">
         <v>3550002</v>
@@ -10770,17 +10830,17 @@
         <v>500</v>
       </c>
       <c r="H181" s="20" t="s">
-        <v>655</v>
+        <v>770</v>
       </c>
       <c r="I181" s="20" t="s">
-        <v>656</v>
+        <v>532</v>
       </c>
       <c r="J181" s="48" t="s">
-        <v>739</v>
+        <v>581</v>
       </c>
       <c r="K181" s="20"/>
       <c r="L181" s="20" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M181" s="20">
         <v>3550003</v>
@@ -10809,19 +10869,19 @@
         <v>500</v>
       </c>
       <c r="H182" s="20" t="s">
-        <v>742</v>
+        <v>771</v>
       </c>
       <c r="I182" s="20" t="s">
         <v>395</v>
       </c>
       <c r="J182" s="48" t="s">
-        <v>657</v>
+        <v>533</v>
       </c>
       <c r="K182" s="20">
         <v>3050301</v>
       </c>
       <c r="L182" s="20" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M182" s="20">
         <v>3550002</v>
@@ -10850,19 +10910,19 @@
         <v>500</v>
       </c>
       <c r="H183" s="20" t="s">
-        <v>658</v>
+        <v>772</v>
       </c>
       <c r="I183" s="20" t="s">
         <v>396</v>
       </c>
       <c r="J183" s="48" t="s">
-        <v>659</v>
+        <v>534</v>
       </c>
       <c r="K183" s="20">
         <v>3550501</v>
       </c>
       <c r="L183" s="20" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M183" s="20">
         <v>3550003</v>
@@ -10891,19 +10951,19 @@
         <v>500</v>
       </c>
       <c r="H184" s="20" t="s">
-        <v>660</v>
+        <v>773</v>
       </c>
       <c r="I184" s="20" t="s">
         <v>397</v>
       </c>
       <c r="J184" s="48" t="s">
-        <v>661</v>
+        <v>535</v>
       </c>
       <c r="K184" s="20">
         <v>3550206</v>
       </c>
       <c r="L184" s="20" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M184" s="20">
         <v>3550002</v>
@@ -10932,19 +10992,19 @@
         <v>500</v>
       </c>
       <c r="H185" s="20" t="s">
-        <v>743</v>
+        <v>774</v>
       </c>
       <c r="I185" s="20" t="s">
         <v>398</v>
       </c>
       <c r="J185" s="48" t="s">
-        <v>662</v>
+        <v>536</v>
       </c>
       <c r="K185" s="20">
         <v>3050301</v>
       </c>
       <c r="L185" s="20" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M185" s="20">
         <v>3550003</v>
@@ -10973,19 +11033,19 @@
         <v>500</v>
       </c>
       <c r="H186" s="20" t="s">
-        <v>729</v>
+        <v>775</v>
       </c>
       <c r="I186" s="20" t="s">
         <v>399</v>
       </c>
       <c r="J186" s="48" t="s">
-        <v>663</v>
+        <v>537</v>
       </c>
       <c r="K186" s="49" t="s">
-        <v>744</v>
+        <v>582</v>
       </c>
       <c r="L186" s="20" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M186" s="20">
         <v>3550001</v>
@@ -11014,10 +11074,10 @@
         <v>500</v>
       </c>
       <c r="H187" s="20" t="s">
-        <v>745</v>
+        <v>776</v>
       </c>
       <c r="I187" s="20" t="s">
-        <v>746</v>
+        <v>583</v>
       </c>
       <c r="J187" s="48" t="s">
         <v>48</v>
@@ -11026,7 +11086,7 @@
         <v>3050301</v>
       </c>
       <c r="L187" s="20" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M187" s="20">
         <v>3550001</v>
@@ -11046,7 +11106,7 @@
         <v>1</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>727</v>
+        <v>578</v>
       </c>
       <c r="F188" s="22">
         <v>1</v>
@@ -11055,19 +11115,19 @@
         <v>500</v>
       </c>
       <c r="H188" s="22" t="s">
-        <v>664</v>
+        <v>686</v>
       </c>
       <c r="I188" s="22" t="s">
-        <v>582</v>
+        <v>490</v>
       </c>
       <c r="J188" s="22" t="s">
-        <v>665</v>
+        <v>538</v>
       </c>
       <c r="K188" s="22">
         <v>3060001</v>
       </c>
       <c r="L188" s="22" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M188" s="22">
         <v>3560001</v>
@@ -11096,19 +11156,19 @@
         <v>500</v>
       </c>
       <c r="H189" s="22" t="s">
-        <v>666</v>
+        <v>736</v>
       </c>
       <c r="I189" s="22" t="s">
-        <v>583</v>
+        <v>491</v>
       </c>
       <c r="J189" s="22" t="s">
-        <v>723</v>
+        <v>574</v>
       </c>
       <c r="K189" s="22">
         <v>3060102</v>
       </c>
       <c r="L189" s="22" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M189" s="22">
         <v>3560002</v>
@@ -11137,17 +11197,17 @@
         <v>500</v>
       </c>
       <c r="H190" s="22" t="s">
-        <v>667</v>
+        <v>737</v>
       </c>
       <c r="I190" s="22" t="s">
-        <v>584</v>
+        <v>492</v>
       </c>
       <c r="J190" s="22" t="s">
-        <v>724</v>
+        <v>575</v>
       </c>
       <c r="K190" s="22"/>
       <c r="L190" s="22" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M190" s="22">
         <v>3560003</v>
@@ -11176,19 +11236,19 @@
         <v>500</v>
       </c>
       <c r="H191" s="22" t="s">
-        <v>668</v>
+        <v>738</v>
       </c>
       <c r="I191" s="22" t="s">
-        <v>585</v>
+        <v>493</v>
       </c>
       <c r="J191" s="22" t="s">
-        <v>728</v>
+        <v>579</v>
       </c>
       <c r="K191" s="24" t="s">
-        <v>565</v>
+        <v>476</v>
       </c>
       <c r="L191" s="22" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M191" s="24">
         <v>3560002</v>
@@ -11217,19 +11277,19 @@
         <v>500</v>
       </c>
       <c r="H192" s="22" t="s">
-        <v>669</v>
+        <v>739</v>
       </c>
       <c r="I192" s="22" t="s">
-        <v>485</v>
+        <v>400</v>
       </c>
       <c r="J192" s="22" t="s">
-        <v>722</v>
+        <v>573</v>
       </c>
       <c r="K192" s="22">
         <v>3560501</v>
       </c>
       <c r="L192" s="22" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M192" s="22">
         <v>3560003</v>
@@ -11258,19 +11318,19 @@
         <v>500</v>
       </c>
       <c r="H193" s="22" t="s">
-        <v>670</v>
+        <v>740</v>
       </c>
       <c r="I193" s="22" t="s">
-        <v>586</v>
+        <v>494</v>
       </c>
       <c r="J193" s="22" t="s">
-        <v>671</v>
+        <v>539</v>
       </c>
       <c r="K193" s="22">
         <v>3060102</v>
       </c>
       <c r="L193" s="22" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M193" s="22">
         <v>3560002</v>
@@ -11299,19 +11359,19 @@
         <v>500</v>
       </c>
       <c r="H194" s="22" t="s">
-        <v>672</v>
+        <v>741</v>
       </c>
       <c r="I194" s="22" t="s">
-        <v>486</v>
+        <v>401</v>
       </c>
       <c r="J194" s="22" t="s">
-        <v>673</v>
+        <v>540</v>
       </c>
       <c r="K194" s="22">
         <v>3060102</v>
       </c>
       <c r="L194" s="22" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M194" s="22">
         <v>3560003</v>
@@ -11340,17 +11400,17 @@
         <v>500</v>
       </c>
       <c r="H195" s="22" t="s">
-        <v>674</v>
+        <v>742</v>
       </c>
       <c r="I195" s="22" t="s">
-        <v>587</v>
+        <v>495</v>
       </c>
       <c r="J195" s="22" t="s">
-        <v>515</v>
+        <v>427</v>
       </c>
       <c r="K195" s="25"/>
       <c r="L195" s="22" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M195" s="22">
         <v>3560004</v>
@@ -11370,7 +11430,7 @@
         <v>1</v>
       </c>
       <c r="E196" s="27" t="s">
-        <v>727</v>
+        <v>578</v>
       </c>
       <c r="F196" s="26">
         <v>1</v>
@@ -11379,19 +11439,19 @@
         <v>500</v>
       </c>
       <c r="H196" s="26" t="s">
-        <v>455</v>
+        <v>693</v>
       </c>
       <c r="I196" s="26" t="s">
-        <v>675</v>
+        <v>541</v>
       </c>
       <c r="J196" s="26" t="s">
-        <v>676</v>
+        <v>542</v>
       </c>
       <c r="K196" s="26">
         <v>3070001</v>
       </c>
       <c r="L196" s="26" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M196" s="26">
         <v>3570001</v>
@@ -11420,19 +11480,19 @@
         <v>500</v>
       </c>
       <c r="H197" s="26" t="s">
-        <v>677</v>
+        <v>743</v>
       </c>
       <c r="I197" s="26" t="s">
-        <v>678</v>
+        <v>543</v>
       </c>
       <c r="J197" s="26" t="s">
-        <v>679</v>
+        <v>544</v>
       </c>
       <c r="K197" s="28" t="s">
-        <v>566</v>
+        <v>477</v>
       </c>
       <c r="L197" s="26" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M197" s="26">
         <v>3570002</v>
@@ -11461,17 +11521,17 @@
         <v>500</v>
       </c>
       <c r="H198" s="26" t="s">
-        <v>680</v>
+        <v>744</v>
       </c>
       <c r="I198" s="26" t="s">
-        <v>681</v>
+        <v>545</v>
       </c>
       <c r="J198" s="26" t="s">
-        <v>682</v>
+        <v>546</v>
       </c>
       <c r="K198" s="26"/>
       <c r="L198" s="26" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M198" s="26">
         <v>3570003</v>
@@ -11500,19 +11560,19 @@
         <v>500</v>
       </c>
       <c r="H199" s="26" t="s">
-        <v>683</v>
+        <v>745</v>
       </c>
       <c r="I199" s="26" t="s">
-        <v>684</v>
+        <v>547</v>
       </c>
       <c r="J199" s="26" t="s">
-        <v>685</v>
+        <v>548</v>
       </c>
       <c r="K199" s="28" t="s">
-        <v>566</v>
+        <v>477</v>
       </c>
       <c r="L199" s="26" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M199" s="26">
         <v>3570002</v>
@@ -11541,19 +11601,19 @@
         <v>500</v>
       </c>
       <c r="H200" s="26" t="s">
-        <v>686</v>
+        <v>746</v>
       </c>
       <c r="I200" s="26" t="s">
-        <v>687</v>
+        <v>549</v>
       </c>
       <c r="J200" s="26" t="s">
-        <v>721</v>
+        <v>572</v>
       </c>
       <c r="K200" s="26">
         <v>3570701</v>
       </c>
       <c r="L200" s="26" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M200" s="26">
         <v>3570003</v>
@@ -11582,19 +11642,19 @@
         <v>500</v>
       </c>
       <c r="H201" s="26" t="s">
-        <v>688</v>
+        <v>747</v>
       </c>
       <c r="I201" s="26" t="s">
-        <v>689</v>
+        <v>550</v>
       </c>
       <c r="J201" s="26" t="s">
-        <v>690</v>
+        <v>551</v>
       </c>
       <c r="K201" s="26">
         <v>3070102</v>
       </c>
       <c r="L201" s="26" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M201" s="26">
         <v>3570002</v>
@@ -11623,19 +11683,19 @@
         <v>500</v>
       </c>
       <c r="H202" s="26" t="s">
-        <v>691</v>
+        <v>748</v>
       </c>
       <c r="I202" s="26" t="s">
-        <v>692</v>
+        <v>552</v>
       </c>
       <c r="J202" s="26" t="s">
-        <v>693</v>
+        <v>553</v>
       </c>
       <c r="K202" s="26">
         <v>3070102</v>
       </c>
       <c r="L202" s="26" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M202" s="26">
         <v>3570003</v>
@@ -11664,17 +11724,17 @@
         <v>500</v>
       </c>
       <c r="H203" s="26" t="s">
-        <v>694</v>
+        <v>749</v>
       </c>
       <c r="I203" s="26" t="s">
-        <v>695</v>
+        <v>554</v>
       </c>
       <c r="J203" s="26" t="s">
-        <v>696</v>
+        <v>555</v>
       </c>
       <c r="K203" s="29"/>
       <c r="L203" s="26" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M203" s="26">
         <v>3570001</v>
@@ -11694,7 +11754,7 @@
         <v>1</v>
       </c>
       <c r="E204" s="31" t="s">
-        <v>727</v>
+        <v>578</v>
       </c>
       <c r="F204" s="30">
         <v>1</v>
@@ -11703,19 +11763,19 @@
         <v>500</v>
       </c>
       <c r="H204" s="30" t="s">
-        <v>697</v>
+        <v>750</v>
       </c>
       <c r="I204" s="30" t="s">
-        <v>698</v>
+        <v>556</v>
       </c>
       <c r="J204" s="30" t="s">
-        <v>699</v>
+        <v>557</v>
       </c>
       <c r="K204" s="30">
         <v>3080001</v>
       </c>
       <c r="L204" s="30" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M204" s="30">
         <v>3580001</v>
@@ -11744,19 +11804,19 @@
         <v>500</v>
       </c>
       <c r="H205" s="30" t="s">
-        <v>700</v>
+        <v>751</v>
       </c>
       <c r="I205" s="30" t="s">
-        <v>701</v>
+        <v>558</v>
       </c>
       <c r="J205" s="30" t="s">
-        <v>702</v>
+        <v>559</v>
       </c>
       <c r="K205" s="32" t="s">
-        <v>556</v>
+        <v>467</v>
       </c>
       <c r="L205" s="30" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M205" s="30">
         <v>3580002</v>
@@ -11785,19 +11845,19 @@
         <v>500</v>
       </c>
       <c r="H206" s="30" t="s">
-        <v>703</v>
+        <v>752</v>
       </c>
       <c r="I206" s="30" t="s">
-        <v>704</v>
+        <v>560</v>
       </c>
       <c r="J206" s="30" t="s">
-        <v>705</v>
+        <v>561</v>
       </c>
       <c r="K206" s="30">
         <v>3080102</v>
       </c>
       <c r="L206" s="30" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M206" s="30">
         <v>3580003</v>
@@ -11826,19 +11886,19 @@
         <v>500</v>
       </c>
       <c r="H207" s="30" t="s">
-        <v>706</v>
+        <v>753</v>
       </c>
       <c r="I207" s="30" t="s">
-        <v>707</v>
+        <v>562</v>
       </c>
       <c r="J207" s="30" t="s">
-        <v>708</v>
+        <v>563</v>
       </c>
       <c r="K207" s="30">
         <v>3080102</v>
       </c>
       <c r="L207" s="30" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M207" s="30">
         <v>3580002</v>
@@ -11867,19 +11927,19 @@
         <v>500</v>
       </c>
       <c r="H208" s="30" t="s">
-        <v>709</v>
+        <v>754</v>
       </c>
       <c r="I208" s="30" t="s">
-        <v>710</v>
+        <v>564</v>
       </c>
       <c r="J208" s="30" t="s">
-        <v>711</v>
+        <v>565</v>
       </c>
       <c r="K208" s="30">
         <v>3080102</v>
       </c>
       <c r="L208" s="30" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M208" s="30">
         <v>3580003</v>
@@ -11908,19 +11968,19 @@
         <v>500</v>
       </c>
       <c r="H209" s="30" t="s">
-        <v>712</v>
+        <v>755</v>
       </c>
       <c r="I209" s="30" t="s">
-        <v>713</v>
+        <v>566</v>
       </c>
       <c r="J209" s="30" t="s">
-        <v>714</v>
+        <v>567</v>
       </c>
       <c r="K209" s="30">
         <v>3080102</v>
       </c>
       <c r="L209" s="30" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M209" s="30">
         <v>3580002</v>
@@ -11949,19 +12009,19 @@
         <v>500</v>
       </c>
       <c r="H210" s="30" t="s">
-        <v>715</v>
+        <v>756</v>
       </c>
       <c r="I210" s="30" t="s">
-        <v>716</v>
+        <v>568</v>
       </c>
       <c r="J210" s="30" t="s">
-        <v>717</v>
+        <v>569</v>
       </c>
       <c r="K210" s="30">
         <v>3080102</v>
       </c>
       <c r="L210" s="30" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M210" s="30">
         <v>3580003</v>
@@ -11990,19 +12050,19 @@
         <v>500</v>
       </c>
       <c r="H211" s="30" t="s">
-        <v>718</v>
+        <v>757</v>
       </c>
       <c r="I211" s="30" t="s">
-        <v>719</v>
+        <v>570</v>
       </c>
       <c r="J211" s="30" t="s">
-        <v>720</v>
+        <v>571</v>
       </c>
       <c r="K211" s="33" t="s">
-        <v>557</v>
+        <v>468</v>
       </c>
       <c r="L211" s="30" t="s">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="M211" s="32">
         <v>3580001</v>
@@ -12940,7 +13000,7 @@
         <v>1010901</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="P23" s="1">
         <v>3051101</v>
@@ -12974,7 +13034,7 @@
         <v>1010902</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="P24" s="1">
         <f>P23+1</f>
@@ -13009,7 +13069,7 @@
         <v>1010903</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
       <c r="P25" s="1">
         <v>3051200</v>
@@ -13040,7 +13100,7 @@
         <v>1010904</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
     </row>
     <row r="27" spans="3:18" x14ac:dyDescent="0.15">
@@ -13068,7 +13128,7 @@
         <v>1010905</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>575</v>
+        <v>483</v>
       </c>
     </row>
     <row r="28" spans="3:18" x14ac:dyDescent="0.15">
@@ -13096,7 +13156,7 @@
         <v>905010101</v>
       </c>
       <c r="O28" s="12" t="s">
-        <v>535</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" spans="3:18" x14ac:dyDescent="0.15">
@@ -13124,7 +13184,7 @@
         <v>905010202</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>536</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" spans="3:18" x14ac:dyDescent="0.15">
@@ -13152,7 +13212,7 @@
         <v>905010302</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>537</v>
+        <v>449</v>
       </c>
     </row>
     <row r="31" spans="3:18" x14ac:dyDescent="0.15">
@@ -13180,7 +13240,7 @@
         <v>905010403</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>538</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" spans="3:18" x14ac:dyDescent="0.15">
@@ -13208,7 +13268,7 @@
         <v>905010503</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>539</v>
+        <v>451</v>
       </c>
     </row>
     <row r="33" spans="3:15" x14ac:dyDescent="0.15">
@@ -13236,7 +13296,7 @@
         <v>905010604</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>540</v>
+        <v>452</v>
       </c>
     </row>
     <row r="34" spans="3:15" x14ac:dyDescent="0.15">
@@ -13264,7 +13324,7 @@
         <v>905010704</v>
       </c>
       <c r="O34" s="12" t="s">
-        <v>542</v>
+        <v>453</v>
       </c>
     </row>
     <row r="35" spans="3:15" x14ac:dyDescent="0.15">
@@ -13292,7 +13352,7 @@
         <v>905010805</v>
       </c>
       <c r="O35" s="12" t="s">
-        <v>544</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" spans="3:15" x14ac:dyDescent="0.15">
@@ -13320,7 +13380,7 @@
         <v>901010101</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>582</v>
+        <v>490</v>
       </c>
     </row>
     <row r="37" spans="3:15" x14ac:dyDescent="0.15">
@@ -13348,7 +13408,7 @@
         <v>901010202</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>583</v>
+        <v>491</v>
       </c>
     </row>
     <row r="38" spans="3:15" x14ac:dyDescent="0.15">
@@ -13376,7 +13436,7 @@
         <v>901010302</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>584</v>
+        <v>492</v>
       </c>
     </row>
     <row r="39" spans="3:15" x14ac:dyDescent="0.15">
@@ -13404,7 +13464,7 @@
         <v>901010403</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>585</v>
+        <v>493</v>
       </c>
     </row>
     <row r="40" spans="3:15" x14ac:dyDescent="0.15">
@@ -13432,7 +13492,7 @@
         <v>901010503</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>485</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" spans="3:15" x14ac:dyDescent="0.15">
@@ -13460,7 +13520,7 @@
         <v>901010604</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>586</v>
+        <v>494</v>
       </c>
     </row>
     <row r="42" spans="3:15" x14ac:dyDescent="0.15">
@@ -13488,7 +13548,7 @@
         <v>901010704</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>486</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" spans="3:15" x14ac:dyDescent="0.15">
@@ -13516,7 +13576,7 @@
         <v>901010805</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>587</v>
+        <v>495</v>
       </c>
     </row>
     <row r="44" spans="3:15" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_v8【迷宫-能力词条】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_v8【迷宫-能力词条】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8226C3-1AA4-4FB7-BDCD-9FEA3B28630D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4ED5C73-E02E-48A8-85B1-A4B143178FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="793">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2499,242 +2499,317 @@
     <t>3050001:4000_3050000:1_9201:3000</t>
   </si>
   <si>
+    <t>3060001:4000_3060000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3060102:12500_9201:5000</t>
+  </si>
+  <si>
+    <t>3060102:17500_9201:10000</t>
+  </si>
+  <si>
+    <t>3060102:20000_9201:15000</t>
+  </si>
+  <si>
+    <t>3060102:22500_9201:22000</t>
+  </si>
+  <si>
+    <t>3060102:25000_9201:30000</t>
+  </si>
+  <si>
+    <t>3060102:27500_9201:40000</t>
+  </si>
+  <si>
+    <t>3070001:3000_3070000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3070102:10000_9201:7000</t>
+  </si>
+  <si>
+    <t>3070102:10000_9201:10000</t>
+  </si>
+  <si>
+    <t>3070102:20000_9201:15000</t>
+  </si>
+  <si>
+    <t>3070102:30000_9201:22000</t>
+  </si>
+  <si>
+    <t>3070102:40000_9201:30000</t>
+  </si>
+  <si>
+    <t>3070102:50000_9201:40000</t>
+  </si>
+  <si>
+    <t>3080001:3000_3080000:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3080102:10000_9201:7000</t>
+  </si>
+  <si>
+    <t>3080102:10000_9201:10000</t>
+  </si>
+  <si>
+    <t>3080102:20000_9201:15000</t>
+  </si>
+  <si>
+    <t>3080102:30000_9201:22000</t>
+  </si>
+  <si>
+    <t>3080102:40000_9201:30000</t>
+  </si>
+  <si>
+    <t>3080102:50000_9201:40000</t>
+  </si>
+  <si>
+    <t>3040202:2000_9201:3000</t>
+  </si>
+  <si>
+    <t>3041102:2000_9201:5000</t>
+  </si>
+  <si>
+    <t>3041102:2000_9201:7000</t>
+  </si>
+  <si>
+    <t>3040202:2000_9201:10000</t>
+  </si>
+  <si>
+    <t>3041102:2000_9201:15000</t>
+  </si>
+  <si>
+    <t>3040202:2000_9201:22000</t>
+  </si>
+  <si>
+    <t>3041001:3000_9201:3000</t>
+  </si>
+  <si>
+    <t>3041001:3000_9201:5000</t>
+  </si>
+  <si>
+    <t>3041001:5000_9201:7000</t>
+  </si>
+  <si>
+    <t>3041001:5000_9201:10000</t>
+  </si>
+  <si>
+    <t>3041001:7000_9201:15000</t>
+  </si>
+  <si>
+    <t>3041001:7000_9201:22000</t>
+  </si>
+  <si>
+    <t>3041001:10000_9201:30000</t>
+  </si>
+  <si>
+    <t>3041001:15000_9201:40000</t>
+  </si>
+  <si>
+    <t>3540100:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3540300:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3540500:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3540700:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3540900:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3541100:1_9201:22000</t>
+  </si>
+  <si>
+    <t>3541300:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3541500:1_9201:40000</t>
+  </si>
+  <si>
+    <t>3541700:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3541900:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3542100:1_9201:22000</t>
+  </si>
+  <si>
+    <t>3542300:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3050301:10000_3550100:1_3551000:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3060301:12500_3560100:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3060102:15000_3560400:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3060701:17500_3560600:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3560501:3_3560800:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3060701:17500_3561300:1_9201:22000</t>
+  </si>
+  <si>
+    <t>3060301:17500_3560503:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3060102:17500_3561000:1_9201:40000</t>
+  </si>
+  <si>
+    <t>3070301:10000_3570100:1_9201:5000</t>
+  </si>
+  <si>
+    <t>3570600:1_3570400:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3070301:10000_3570800:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3570701:3_3570503:2500_9201:15000</t>
+  </si>
+  <si>
+    <t>3571000:1_3570201:3000_9201:22000</t>
+  </si>
+  <si>
+    <t>3070301:40000_3570703:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3570201:30000_3571200:1_9201:40000</t>
+  </si>
+  <si>
+    <t>3080001:3000_3080000:1_3580100:1_9201:3000</t>
+  </si>
+  <si>
+    <t>3080301:10000_3080701:4000_9201:5000</t>
+  </si>
+  <si>
+    <t>3580400:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3080701:5000_3580600:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3580501:3_3580207:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3080701:6000_3580800:1_9201:22000</t>
+  </si>
+  <si>
+    <t>3080301:40000_3580503:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3080301:50000_3580208:6700_9201:40000</t>
+  </si>
+  <si>
+    <t>3040102:3000_9201:3000</t>
+  </si>
+  <si>
+    <t>3040102:5000_9201:5000</t>
+  </si>
+  <si>
+    <t>3040102:10000_9201:10000</t>
+  </si>
+  <si>
+    <t>3040102:15000_9201:15000</t>
+  </si>
+  <si>
+    <t>3041501:1_9201:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:5000_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550400:1_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:10000_3551101:100000_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550501:3_3551400:1_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550206:1500_3550800:1_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:10000_3550703:1_9201:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550206:1500_3551200:1_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:20000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:9000_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:12000_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:15000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:4000_9201:5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:6000_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:7000_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:8000_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:9000_9201:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:10000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:11000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:12000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:4000_9201:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>3050301:6000_3550100:1_3551000:1_9201:5000</t>
-  </si>
-  <si>
-    <t>3060001:4000_3060000:1_9201:3000</t>
-  </si>
-  <si>
-    <t>3060102:12500_9201:5000</t>
-  </si>
-  <si>
-    <t>3060102:17500_9201:10000</t>
-  </si>
-  <si>
-    <t>3060102:20000_9201:15000</t>
-  </si>
-  <si>
-    <t>3060102:22500_9201:22000</t>
-  </si>
-  <si>
-    <t>3060102:25000_9201:30000</t>
-  </si>
-  <si>
-    <t>3060102:27500_9201:40000</t>
-  </si>
-  <si>
-    <t>3070001:3000_3070000:1_9201:3000</t>
-  </si>
-  <si>
-    <t>3070102:10000_9201:7000</t>
-  </si>
-  <si>
-    <t>3070102:10000_9201:10000</t>
-  </si>
-  <si>
-    <t>3070102:20000_9201:15000</t>
-  </si>
-  <si>
-    <t>3070102:30000_9201:22000</t>
-  </si>
-  <si>
-    <t>3070102:40000_9201:30000</t>
-  </si>
-  <si>
-    <t>3070102:50000_9201:40000</t>
-  </si>
-  <si>
-    <t>3080001:3000_3080000:1_9201:3000</t>
-  </si>
-  <si>
-    <t>3080102:10000_9201:7000</t>
-  </si>
-  <si>
-    <t>3080102:10000_9201:10000</t>
-  </si>
-  <si>
-    <t>3080102:20000_9201:15000</t>
-  </si>
-  <si>
-    <t>3080102:30000_9201:22000</t>
-  </si>
-  <si>
-    <t>3080102:40000_9201:30000</t>
-  </si>
-  <si>
-    <t>3080102:50000_9201:40000</t>
-  </si>
-  <si>
-    <t>3040202:2000_9201:3000</t>
-  </si>
-  <si>
-    <t>3041102:2000_9201:5000</t>
-  </si>
-  <si>
-    <t>3041102:2000_9201:7000</t>
-  </si>
-  <si>
-    <t>3040202:2000_9201:10000</t>
-  </si>
-  <si>
-    <t>3041102:2000_9201:15000</t>
-  </si>
-  <si>
-    <t>3040202:2000_9201:22000</t>
-  </si>
-  <si>
-    <t>3040102:4000_9201:30000</t>
-  </si>
-  <si>
-    <t>3040102:4000_3041201:1000_9201:5000</t>
-  </si>
-  <si>
-    <t>3041001:3000_9201:3000</t>
-  </si>
-  <si>
-    <t>3041001:3000_9201:5000</t>
-  </si>
-  <si>
-    <t>3041001:5000_9201:7000</t>
-  </si>
-  <si>
-    <t>3041001:5000_9201:10000</t>
-  </si>
-  <si>
-    <t>3041001:7000_9201:15000</t>
-  </si>
-  <si>
-    <t>3041001:7000_9201:22000</t>
-  </si>
-  <si>
-    <t>3041001:10000_9201:30000</t>
-  </si>
-  <si>
-    <t>3041001:15000_9201:40000</t>
-  </si>
-  <si>
-    <t>3540100:1_9201:3000</t>
-  </si>
-  <si>
-    <t>3540300:1_9201:5000</t>
-  </si>
-  <si>
-    <t>3540500:1_9201:7000</t>
-  </si>
-  <si>
-    <t>3540700:1_9201:10000</t>
-  </si>
-  <si>
-    <t>3540900:1_9201:15000</t>
-  </si>
-  <si>
-    <t>3541100:1_9201:22000</t>
-  </si>
-  <si>
-    <t>3541300:1_9201:30000</t>
-  </si>
-  <si>
-    <t>3541500:1_9201:40000</t>
-  </si>
-  <si>
-    <t>3541700:1_9201:10000</t>
-  </si>
-  <si>
-    <t>3541900:1_9201:15000</t>
-  </si>
-  <si>
-    <t>3542100:1_9201:22000</t>
-  </si>
-  <si>
-    <t>3542300:1_9201:30000</t>
-  </si>
-  <si>
-    <t>3050301:10000_3550100:1_3551000:1_9201:5000</t>
-  </si>
-  <si>
-    <t>3060301:12500_3560100:1_9201:5000</t>
-  </si>
-  <si>
-    <t>3060102:15000_3560400:1_9201:7000</t>
-  </si>
-  <si>
-    <t>3060701:17500_3560600:1_9201:10000</t>
-  </si>
-  <si>
-    <t>3560501:3_3560800:1_9201:15000</t>
-  </si>
-  <si>
-    <t>3060701:17500_3561300:1_9201:22000</t>
-  </si>
-  <si>
-    <t>3060301:17500_3560503:1_9201:30000</t>
-  </si>
-  <si>
-    <t>3060102:17500_3561000:1_9201:40000</t>
-  </si>
-  <si>
-    <t>3070301:10000_3570100:1_9201:5000</t>
-  </si>
-  <si>
-    <t>3570600:1_3570400:1_9201:7000</t>
-  </si>
-  <si>
-    <t>3070301:10000_3570800:1_9201:10000</t>
-  </si>
-  <si>
-    <t>3570701:3_3570503:2500_9201:15000</t>
-  </si>
-  <si>
-    <t>3571000:1_3570201:3000_9201:22000</t>
-  </si>
-  <si>
-    <t>3070301:40000_3570703:1_9201:30000</t>
-  </si>
-  <si>
-    <t>3570201:30000_3571200:1_9201:40000</t>
-  </si>
-  <si>
-    <t>3080001:3000_3080000:1_3580100:1_9201:3000</t>
-  </si>
-  <si>
-    <t>3080301:10000_3080701:4000_9201:5000</t>
-  </si>
-  <si>
-    <t>3580400:1_9201:7000</t>
-  </si>
-  <si>
-    <t>3080701:5000_3580600:1_9201:10000</t>
-  </si>
-  <si>
-    <t>3580501:3_3580207:1_9201:15000</t>
-  </si>
-  <si>
-    <t>3080701:6000_3580800:1_9201:22000</t>
-  </si>
-  <si>
-    <t>3080301:40000_3580503:1_9201:30000</t>
-  </si>
-  <si>
-    <t>3080301:50000_3580208:6700_9201:40000</t>
-  </si>
-  <si>
-    <t>3040102:3000_9201:3000</t>
-  </si>
-  <si>
-    <t>3040102:5000_9201:5000</t>
-  </si>
-  <si>
-    <t>3040102:10000_9201:10000</t>
-  </si>
-  <si>
-    <t>3040102:15000_9201:15000</t>
-  </si>
-  <si>
-    <t>3041501:1_9201:3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:5000_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:4000_3041201:600_9201:5000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2742,19 +2817,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3040102:5000_3041201:500_9201:7000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:6000_3041201:500_9201:8000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:7000_3041201:500_9201:9000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:8000_3041201:500_9201:10000</t>
+    <t>3041501:1_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3041501:2_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:6000_3041201:300_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:7000_3041201:300_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:8000_3041201:500_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:9000_3041201:300_9201:10000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2762,91 +2845,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3550400:1_9201:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:10000_3551101:100000_9201:7000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3550501:3_3551400:1_9201:8000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3550206:1500_3550800:1_9201:9000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:10000_3550703:1_9201:10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3550206:1500_3551200:1_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:20000_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:9000_9201:7000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3550501:2_9201:8000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:12000_9201:9000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3550501:2_9201:10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:15000_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3041501:1_9201:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3041501:2_9201:9000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:4000_9201:5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:6000_9201:7000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:7000_9201:8000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:8000_9201:9000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:9000_9201:10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:10000_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:11000_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:12000_9201:12000</t>
+    <t>3050301:3000_3550400:1_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:4500_3550501:2_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:6000_3550501:2_9201:10000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3676,7 +3683,7 @@
         <v>100</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>132</v>
@@ -3717,7 +3724,7 @@
         <v>100</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>132</v>
@@ -3799,7 +3806,7 @@
         <v>100</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>132</v>
@@ -3840,7 +3847,7 @@
         <v>100</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>132</v>
@@ -4537,7 +4544,7 @@
         <v>100</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>483</v>
@@ -4578,7 +4585,7 @@
         <v>100</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>483</v>
@@ -4619,7 +4626,7 @@
         <v>100</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>483</v>
@@ -4660,7 +4667,7 @@
         <v>100</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>497</v>
@@ -4701,7 +4708,7 @@
         <v>100</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>497</v>
@@ -4742,7 +4749,7 @@
         <v>100</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>497</v>
@@ -4783,7 +4790,7 @@
         <v>100</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>497</v>
@@ -4824,7 +4831,7 @@
         <v>100</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>497</v>
@@ -4865,7 +4872,7 @@
         <v>100</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>497</v>
@@ -4906,7 +4913,7 @@
         <v>100</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>497</v>
@@ -4947,7 +4954,7 @@
         <v>100</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>497</v>
@@ -4988,7 +4995,7 @@
         <v>100</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>497</v>
@@ -8145,7 +8152,7 @@
         <v>500</v>
       </c>
       <c r="H114" s="20" t="s">
-        <v>685</v>
+        <v>780</v>
       </c>
       <c r="I114" s="20" t="s">
         <v>393</v>
@@ -8186,7 +8193,7 @@
         <v>500</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>770</v>
+        <v>790</v>
       </c>
       <c r="I115" s="20" t="s">
         <v>532</v>
@@ -8225,7 +8232,7 @@
         <v>500</v>
       </c>
       <c r="H116" s="20" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="I116" s="20" t="s">
         <v>395</v>
@@ -8266,7 +8273,7 @@
         <v>500</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>778</v>
+        <v>791</v>
       </c>
       <c r="I117" s="20" t="s">
         <v>396</v>
@@ -8307,7 +8314,7 @@
         <v>500</v>
       </c>
       <c r="H118" s="20" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="I118" s="20" t="s">
         <v>397</v>
@@ -8348,7 +8355,7 @@
         <v>500</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="I119" s="20" t="s">
         <v>398</v>
@@ -8389,7 +8396,7 @@
         <v>500</v>
       </c>
       <c r="H120" s="20" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="I120" s="20" t="s">
         <v>399</v>
@@ -8430,7 +8437,7 @@
         <v>500</v>
       </c>
       <c r="H121" s="22" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="I121" s="22" t="s">
         <v>405</v>
@@ -8471,7 +8478,7 @@
         <v>500</v>
       </c>
       <c r="H122" s="22" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="I122" s="22" t="s">
         <v>403</v>
@@ -8551,7 +8558,7 @@
         <v>500</v>
       </c>
       <c r="H124" s="22" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="I124" s="22" t="s">
         <v>404</v>
@@ -8592,7 +8599,7 @@
         <v>500</v>
       </c>
       <c r="H125" s="22" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="I125" s="22" t="s">
         <v>400</v>
@@ -8631,7 +8638,7 @@
         <v>500</v>
       </c>
       <c r="H126" s="22" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="I126" s="22" t="s">
         <v>406</v>
@@ -8672,7 +8679,7 @@
         <v>500</v>
       </c>
       <c r="H127" s="22" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="I127" s="22" t="s">
         <v>401</v>
@@ -8713,7 +8720,7 @@
         <v>500</v>
       </c>
       <c r="H128" s="22" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="I128" s="22" t="s">
         <v>407</v>
@@ -8752,7 +8759,7 @@
         <v>500</v>
       </c>
       <c r="H129" s="26" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I129" s="26" t="s">
         <v>402</v>
@@ -8834,7 +8841,7 @@
         <v>500</v>
       </c>
       <c r="H131" s="26" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="I131" s="26" t="s">
         <v>411</v>
@@ -8873,7 +8880,7 @@
         <v>500</v>
       </c>
       <c r="H132" s="26" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="I132" s="26" t="s">
         <v>409</v>
@@ -8914,7 +8921,7 @@
         <v>500</v>
       </c>
       <c r="H133" s="26" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="I133" s="26" t="s">
         <v>410</v>
@@ -8953,7 +8960,7 @@
         <v>500</v>
       </c>
       <c r="H134" s="26" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="I134" s="26" t="s">
         <v>504</v>
@@ -8994,7 +9001,7 @@
         <v>500</v>
       </c>
       <c r="H135" s="26" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="I135" s="26" t="s">
         <v>412</v>
@@ -9035,7 +9042,7 @@
         <v>500</v>
       </c>
       <c r="H136" s="26" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="I136" s="26" t="s">
         <v>413</v>
@@ -9074,7 +9081,7 @@
         <v>500</v>
       </c>
       <c r="H137" s="30" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="I137" s="30" t="s">
         <v>414</v>
@@ -9156,7 +9163,7 @@
         <v>500</v>
       </c>
       <c r="H139" s="30" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="I139" s="30" t="s">
         <v>419</v>
@@ -9197,7 +9204,7 @@
         <v>500</v>
       </c>
       <c r="H140" s="30" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="I140" s="30" t="s">
         <v>417</v>
@@ -9238,7 +9245,7 @@
         <v>500</v>
       </c>
       <c r="H141" s="30" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="I141" s="30" t="s">
         <v>420</v>
@@ -9279,7 +9286,7 @@
         <v>500</v>
       </c>
       <c r="H142" s="30" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="I142" s="30" t="s">
         <v>421</v>
@@ -9320,7 +9327,7 @@
         <v>500</v>
       </c>
       <c r="H143" s="30" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="I143" s="30" t="s">
         <v>422</v>
@@ -9361,7 +9368,7 @@
         <v>500</v>
       </c>
       <c r="H144" s="30" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="I144" s="30" t="s">
         <v>418</v>
@@ -9402,7 +9409,7 @@
         <v>500</v>
       </c>
       <c r="H145" s="36" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I145" s="34" t="s">
         <v>440</v>
@@ -9443,7 +9450,7 @@
         <v>500</v>
       </c>
       <c r="H146" s="36" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="I146" s="34" t="s">
         <v>424</v>
@@ -9484,7 +9491,7 @@
         <v>500</v>
       </c>
       <c r="H147" s="36" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="I147" s="34" t="s">
         <v>425</v>
@@ -9525,7 +9532,7 @@
         <v>500</v>
       </c>
       <c r="H148" s="36" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="I148" s="34" t="s">
         <v>423</v>
@@ -9564,7 +9571,7 @@
         <v>500</v>
       </c>
       <c r="H149" s="36" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="I149" s="34" t="s">
         <v>445</v>
@@ -9605,7 +9612,7 @@
         <v>500</v>
       </c>
       <c r="H150" s="36" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="I150" s="34" t="s">
         <v>426</v>
@@ -9644,7 +9651,7 @@
         <v>500</v>
       </c>
       <c r="H151" s="39" t="s">
-        <v>713</v>
+        <v>779</v>
       </c>
       <c r="I151" s="37" t="s">
         <v>447</v>
@@ -9685,7 +9692,7 @@
         <v>500</v>
       </c>
       <c r="H152" s="39" t="s">
-        <v>714</v>
+        <v>781</v>
       </c>
       <c r="I152" s="37" t="s">
         <v>448</v>
@@ -9726,7 +9733,7 @@
         <v>500</v>
       </c>
       <c r="H153" s="39" t="s">
-        <v>764</v>
+        <v>782</v>
       </c>
       <c r="I153" s="37" t="s">
         <v>449</v>
@@ -9767,7 +9774,7 @@
         <v>500</v>
       </c>
       <c r="H154" s="39" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="I154" s="37" t="s">
         <v>450</v>
@@ -9806,7 +9813,7 @@
         <v>500</v>
       </c>
       <c r="H155" s="39" t="s">
-        <v>766</v>
+        <v>786</v>
       </c>
       <c r="I155" s="37" t="s">
         <v>451</v>
@@ -9845,7 +9852,7 @@
         <v>500</v>
       </c>
       <c r="H156" s="39" t="s">
-        <v>767</v>
+        <v>787</v>
       </c>
       <c r="I156" s="37" t="s">
         <v>591</v>
@@ -9886,7 +9893,7 @@
         <v>500</v>
       </c>
       <c r="H157" s="39" t="s">
-        <v>768</v>
+        <v>788</v>
       </c>
       <c r="I157" s="37" t="s">
         <v>453</v>
@@ -9925,7 +9932,7 @@
         <v>500</v>
       </c>
       <c r="H158" s="39" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
       <c r="I158" s="37" t="s">
         <v>455</v>
@@ -9964,7 +9971,7 @@
         <v>500</v>
       </c>
       <c r="H159" s="43" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="I159" s="41" t="s">
         <v>470</v>
@@ -10005,7 +10012,7 @@
         <v>500</v>
       </c>
       <c r="H160" s="43" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="I160" s="41" t="s">
         <v>457</v>
@@ -10044,7 +10051,7 @@
         <v>500</v>
       </c>
       <c r="H161" s="43" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="I161" s="41" t="s">
         <v>459</v>
@@ -10083,7 +10090,7 @@
         <v>500</v>
       </c>
       <c r="H162" s="43" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="I162" s="41" t="s">
         <v>460</v>
@@ -10122,7 +10129,7 @@
         <v>500</v>
       </c>
       <c r="H163" s="43" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="I163" s="41" t="s">
         <v>462</v>
@@ -10161,7 +10168,7 @@
         <v>500</v>
       </c>
       <c r="H164" s="43" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="I164" s="41" t="s">
         <v>463</v>
@@ -10200,7 +10207,7 @@
         <v>500</v>
       </c>
       <c r="H165" s="43" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="I165" s="41" t="s">
         <v>465</v>
@@ -10241,7 +10248,7 @@
         <v>500</v>
       </c>
       <c r="H166" s="43" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="I166" s="41" t="s">
         <v>466</v>
@@ -10280,7 +10287,7 @@
         <v>1</v>
       </c>
       <c r="H167" s="45" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="I167" s="45" t="s">
         <v>506</v>
@@ -10319,7 +10326,7 @@
         <v>1</v>
       </c>
       <c r="H168" s="45" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="I168" s="45" t="s">
         <v>507</v>
@@ -10358,7 +10365,7 @@
         <v>1</v>
       </c>
       <c r="H169" s="45" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="I169" s="45" t="s">
         <v>508</v>
@@ -10397,7 +10404,7 @@
         <v>1</v>
       </c>
       <c r="H170" s="45" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="I170" s="45" t="s">
         <v>509</v>
@@ -10436,7 +10443,7 @@
         <v>1</v>
       </c>
       <c r="H171" s="45" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="I171" s="45" t="s">
         <v>510</v>
@@ -10475,7 +10482,7 @@
         <v>1</v>
       </c>
       <c r="H172" s="45" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="I172" s="45" t="s">
         <v>511</v>
@@ -10514,7 +10521,7 @@
         <v>1</v>
       </c>
       <c r="H173" s="45" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="I173" s="45" t="s">
         <v>512</v>
@@ -10553,7 +10560,7 @@
         <v>1</v>
       </c>
       <c r="H174" s="45" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="I174" s="45" t="s">
         <v>513</v>
@@ -10592,7 +10599,7 @@
         <v>1</v>
       </c>
       <c r="H175" s="45" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="I175" s="45" t="s">
         <v>514</v>
@@ -10631,7 +10638,7 @@
         <v>1</v>
       </c>
       <c r="H176" s="45" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="I176" s="45" t="s">
         <v>515</v>
@@ -10670,7 +10677,7 @@
         <v>1</v>
       </c>
       <c r="H177" s="45" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="I177" s="45" t="s">
         <v>516</v>
@@ -10709,7 +10716,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="45" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="I178" s="45" t="s">
         <v>517</v>
@@ -10789,7 +10796,7 @@
         <v>500</v>
       </c>
       <c r="H180" s="20" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="I180" s="20" t="s">
         <v>393</v>
@@ -10830,7 +10837,7 @@
         <v>500</v>
       </c>
       <c r="H181" s="20" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="I181" s="20" t="s">
         <v>532</v>
@@ -10869,7 +10876,7 @@
         <v>500</v>
       </c>
       <c r="H182" s="20" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="I182" s="20" t="s">
         <v>395</v>
@@ -10910,7 +10917,7 @@
         <v>500</v>
       </c>
       <c r="H183" s="20" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="I183" s="20" t="s">
         <v>396</v>
@@ -10951,7 +10958,7 @@
         <v>500</v>
       </c>
       <c r="H184" s="20" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="I184" s="20" t="s">
         <v>397</v>
@@ -10992,7 +10999,7 @@
         <v>500</v>
       </c>
       <c r="H185" s="20" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="I185" s="20" t="s">
         <v>398</v>
@@ -11033,7 +11040,7 @@
         <v>500</v>
       </c>
       <c r="H186" s="20" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="I186" s="20" t="s">
         <v>399</v>
@@ -11074,7 +11081,7 @@
         <v>500</v>
       </c>
       <c r="H187" s="20" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="I187" s="20" t="s">
         <v>583</v>
@@ -11115,7 +11122,7 @@
         <v>500</v>
       </c>
       <c r="H188" s="22" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="I188" s="22" t="s">
         <v>490</v>
@@ -11156,7 +11163,7 @@
         <v>500</v>
       </c>
       <c r="H189" s="22" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="I189" s="22" t="s">
         <v>491</v>
@@ -11197,7 +11204,7 @@
         <v>500</v>
       </c>
       <c r="H190" s="22" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="I190" s="22" t="s">
         <v>492</v>
@@ -11236,7 +11243,7 @@
         <v>500</v>
       </c>
       <c r="H191" s="22" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="I191" s="22" t="s">
         <v>493</v>
@@ -11277,7 +11284,7 @@
         <v>500</v>
       </c>
       <c r="H192" s="22" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="I192" s="22" t="s">
         <v>400</v>
@@ -11318,7 +11325,7 @@
         <v>500</v>
       </c>
       <c r="H193" s="22" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="I193" s="22" t="s">
         <v>494</v>
@@ -11359,7 +11366,7 @@
         <v>500</v>
       </c>
       <c r="H194" s="22" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="I194" s="22" t="s">
         <v>401</v>
@@ -11400,7 +11407,7 @@
         <v>500</v>
       </c>
       <c r="H195" s="22" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="I195" s="22" t="s">
         <v>495</v>
@@ -11439,7 +11446,7 @@
         <v>500</v>
       </c>
       <c r="H196" s="26" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I196" s="26" t="s">
         <v>541</v>
@@ -11480,7 +11487,7 @@
         <v>500</v>
       </c>
       <c r="H197" s="26" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="I197" s="26" t="s">
         <v>543</v>
@@ -11521,7 +11528,7 @@
         <v>500</v>
       </c>
       <c r="H198" s="26" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="I198" s="26" t="s">
         <v>545</v>
@@ -11560,7 +11567,7 @@
         <v>500</v>
       </c>
       <c r="H199" s="26" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="I199" s="26" t="s">
         <v>547</v>
@@ -11601,7 +11608,7 @@
         <v>500</v>
       </c>
       <c r="H200" s="26" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="I200" s="26" t="s">
         <v>549</v>
@@ -11642,7 +11649,7 @@
         <v>500</v>
       </c>
       <c r="H201" s="26" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="I201" s="26" t="s">
         <v>550</v>
@@ -11683,7 +11690,7 @@
         <v>500</v>
       </c>
       <c r="H202" s="26" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="I202" s="26" t="s">
         <v>552</v>
@@ -11724,7 +11731,7 @@
         <v>500</v>
       </c>
       <c r="H203" s="26" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="I203" s="26" t="s">
         <v>554</v>
@@ -11763,7 +11770,7 @@
         <v>500</v>
       </c>
       <c r="H204" s="30" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="I204" s="30" t="s">
         <v>556</v>
@@ -11804,7 +11811,7 @@
         <v>500</v>
       </c>
       <c r="H205" s="30" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="I205" s="30" t="s">
         <v>558</v>
@@ -11845,7 +11852,7 @@
         <v>500</v>
       </c>
       <c r="H206" s="30" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="I206" s="30" t="s">
         <v>560</v>
@@ -11886,7 +11893,7 @@
         <v>500</v>
       </c>
       <c r="H207" s="30" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="I207" s="30" t="s">
         <v>562</v>
@@ -11927,7 +11934,7 @@
         <v>500</v>
       </c>
       <c r="H208" s="30" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="I208" s="30" t="s">
         <v>564</v>
@@ -11968,7 +11975,7 @@
         <v>500</v>
       </c>
       <c r="H209" s="30" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="I209" s="30" t="s">
         <v>566</v>
@@ -12009,7 +12016,7 @@
         <v>500</v>
       </c>
       <c r="H210" s="30" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="I210" s="30" t="s">
         <v>568</v>
@@ -12050,7 +12057,7 @@
         <v>500</v>
       </c>
       <c r="H211" s="30" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="I211" s="30" t="s">
         <v>570</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_v8【迷宫-能力词条】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_v8【迷宫-能力词条】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734CA064-7D74-4143-A8CE-0AA6DFF5CF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091082FE-7366-48B9-9FA5-349B0FA3D6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_affix_v8" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="828">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1973,9 +1973,6 @@
     <t>受到持续伤害提高</t>
   </si>
   <si>
-    <t>移动速度提高</t>
-  </si>
-  <si>
     <t>0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2010,9 +2007,6 @@
     <t>受到持续伤害提高5%，持续4秒，最多叠加3层</t>
   </si>
   <si>
-    <t>移动速度提高5%，持续4秒，最多叠加3层</t>
-  </si>
-  <si>
     <t>受到伤害提高5%，持续4秒，最多叠加3层</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2182,14 +2176,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>冰元素伤害+%s，攻击有几率使目标冰冻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放冰霜新星需要的攻击-%s次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3040102,3041201</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2206,10 +2192,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每攻击12次释放1次冰霜新星，造成冰元素伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>强化锐眼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2631,9 +2613,6 @@
     <t>3542100:1_9201:22000</t>
   </si>
   <si>
-    <t>3542300:1_9201:30000</t>
-  </si>
-  <si>
     <t>3050301:10000_3550100:1_3551000:1_9201:5000</t>
   </si>
   <si>
@@ -2679,187 +2658,347 @@
     <t>3570201:30000_3571200:1_9201:40000</t>
   </si>
   <si>
+    <t>3080301:10000_3080701:4000_9201:5000</t>
+  </si>
+  <si>
+    <t>3580400:1_9201:7000</t>
+  </si>
+  <si>
+    <t>3080701:5000_3580600:1_9201:10000</t>
+  </si>
+  <si>
+    <t>3580501:3_3580207:1_9201:15000</t>
+  </si>
+  <si>
+    <t>3080701:6000_3580800:1_9201:22000</t>
+  </si>
+  <si>
+    <t>3080301:40000_3580503:1_9201:30000</t>
+  </si>
+  <si>
+    <t>3080301:50000_3580208:6700_9201:40000</t>
+  </si>
+  <si>
+    <t>3040102:3000_9201:3000</t>
+  </si>
+  <si>
+    <t>3040102:5000_9201:5000</t>
+  </si>
+  <si>
+    <t>3040102:10000_9201:10000</t>
+  </si>
+  <si>
+    <t>3040102:15000_9201:15000</t>
+  </si>
+  <si>
+    <t>3041501:1_9201:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:5000_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550400:1_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:10000_3551101:100000_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550501:3_3551400:1_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550206:1500_3550800:1_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3550206:1500_3551200:1_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:20000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:4000_9201:5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:6000_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:7000_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:8000_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:9000_9201:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:10000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:11000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:12000_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:4000_9201:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:4000_3041201:600_9201:5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:5000_3041301:2500_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3041501:1_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3041501:2_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:6000_3041201:300_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:7000_3041201:300_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:8000_3041201:500_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:9000_3041201:300_9201:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:10000_3041201:500_9201:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3050301:10000_3550600:1_9201:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰元素伤害+%s，冰霜新星释放次数+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放冰霜新星需要的攻击-%s次，冰霜新星必定使目标冰冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:4000_9201:5000</t>
+  </si>
+  <si>
+    <t>3040102:5000_9201:5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:6000_9201:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:7000_9201:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:8000_9201:8000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:9000_9201:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3040102:10000_9201:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5500100:1_9201:30000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每隔8秒获得自身生命上限20%的护盾，持续4秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击回10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击回2%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击回效果提高30%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷电技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷电目标+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷电伤害+30%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷电目标-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷电伤害-10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹数量+4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加1次60%伤害的冰弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>3080001:3000_3080000:1_3580100:1_9201:3000</t>
-  </si>
-  <si>
-    <t>3080301:10000_3080701:4000_9201:5000</t>
-  </si>
-  <si>
-    <t>3580400:1_9201:7000</t>
-  </si>
-  <si>
-    <t>3080701:5000_3580600:1_9201:10000</t>
-  </si>
-  <si>
-    <t>3580501:3_3580207:1_9201:15000</t>
-  </si>
-  <si>
-    <t>3080701:6000_3580800:1_9201:22000</t>
-  </si>
-  <si>
-    <t>3080301:40000_3580503:1_9201:30000</t>
-  </si>
-  <si>
-    <t>3080301:50000_3580208:6700_9201:40000</t>
-  </si>
-  <si>
-    <t>3040102:3000_9201:3000</t>
-  </si>
-  <si>
-    <t>3040102:5000_9201:5000</t>
-  </si>
-  <si>
-    <t>3040102:10000_9201:10000</t>
-  </si>
-  <si>
-    <t>3040102:15000_9201:15000</t>
-  </si>
-  <si>
-    <t>3041501:1_9201:3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:5000_9201:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3550400:1_9201:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:10000_3551101:100000_9201:7000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3550501:3_3551400:1_9201:8000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3550206:1500_3550800:1_9201:9000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3550206:1500_3551200:1_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:20000_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:9000_9201:7000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:12000_9201:9000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:15000_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:4000_9201:5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:6000_9201:7000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:7000_9201:8000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:8000_9201:9000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:9000_9201:10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:10000_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:11000_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:12000_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:4000_9201:3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:6000_3550100:1_3551000:1_9201:5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:4000_3041201:600_9201:5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:5000_3041301:2500_9201:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3041501:1_9201:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3041501:2_9201:9000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:6000_3041201:300_9201:7000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:7000_3041201:300_9201:8000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:8000_3041201:500_9201:9000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:9000_3041201:300_9201:10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3040102:10000_3041201:500_9201:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:3000_3550400:1_9201:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:4500_3550501:2_9201:8000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3050301:10000_3550600:1_9201:10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰元素伤害+%s，冰霜新星释放次数+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰霜新星释放次数+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3551200:1_9201:10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放冰霜新星需要的攻击-%s次，冰霜新星必定使目标冰冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592200:1_3592201:10_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592200:1_3592202:200_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592300:1_3592401:3000_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000100:1_5000101:1_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100100:1_5100101:1_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200100:1_5200101:1_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200300:1_5200301:2_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200500:1_5200501:3000_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200300:1_5200301:-1_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200500:1_5200501:-1000_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000300:1_5000301:4_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000500:1_5000501:6000_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000700:1_5000701:90_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹伤害+60%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹范围+90°</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001300:1_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000900:1_5000901:1_5001101:-4000_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹命中后产生冰爆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石范围+0.3米</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100300:1_5100301:300_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石伤害+60%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100500:1_5100501:6000_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石数量+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100700:1_5100701:2_9201:1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石爆炸后产生额外半径1.25米、60%伤害的冲击波</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100900:1_5100901:1250_5100902:-4000_9201:1000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3508,7 +3647,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031E3EC7-FCFA-4672-97FA-23C24342A33C}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M211"/>
+  <dimension ref="A1:M230"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5" style="16" bestFit="1" customWidth="1"/>
@@ -3518,7 +3657,7 @@
     <col min="5" max="5" width="17.25" style="47" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.875" style="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="39.375" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.875" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="37.875" style="16" customWidth="1"/>
     <col min="11" max="11" width="18.875" style="16" bestFit="1" customWidth="1"/>
@@ -3689,7 +3828,7 @@
         <v>100</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>132</v>
@@ -3730,7 +3869,7 @@
         <v>100</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>132</v>
@@ -3771,7 +3910,7 @@
         <v>100</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>132</v>
@@ -3812,7 +3951,7 @@
         <v>100</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>132</v>
@@ -3853,7 +3992,7 @@
         <v>100</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>132</v>
@@ -3894,7 +4033,7 @@
         <v>100</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>133</v>
@@ -3935,7 +4074,7 @@
         <v>100</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>134</v>
@@ -3976,7 +4115,7 @@
         <v>100</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>134</v>
@@ -4017,7 +4156,7 @@
         <v>100</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>134</v>
@@ -4058,7 +4197,7 @@
         <v>100</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>134</v>
@@ -4099,7 +4238,7 @@
         <v>100</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>134</v>
@@ -4140,7 +4279,7 @@
         <v>100</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>136</v>
@@ -4181,7 +4320,7 @@
         <v>100</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>136</v>
@@ -4222,7 +4361,7 @@
         <v>100</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>136</v>
@@ -4263,7 +4402,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>136</v>
@@ -4304,7 +4443,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>136</v>
@@ -4345,7 +4484,7 @@
         <v>100</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>137</v>
@@ -4386,7 +4525,7 @@
         <v>100</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>137</v>
@@ -4427,7 +4566,7 @@
         <v>100</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>137</v>
@@ -4468,7 +4607,7 @@
         <v>100</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>137</v>
@@ -4509,7 +4648,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>137</v>
@@ -4550,7 +4689,7 @@
         <v>100</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>483</v>
@@ -4591,7 +4730,7 @@
         <v>100</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>483</v>
@@ -4632,7 +4771,7 @@
         <v>100</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>483</v>
@@ -4673,7 +4812,7 @@
         <v>100</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>497</v>
@@ -4714,7 +4853,7 @@
         <v>100</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>497</v>
@@ -4755,7 +4894,7 @@
         <v>100</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>497</v>
@@ -4796,7 +4935,7 @@
         <v>100</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>497</v>
@@ -4837,7 +4976,7 @@
         <v>100</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>497</v>
@@ -4878,7 +5017,7 @@
         <v>100</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>497</v>
@@ -4919,7 +5058,7 @@
         <v>100</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>497</v>
@@ -4960,7 +5099,7 @@
         <v>100</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>497</v>
@@ -5001,7 +5140,7 @@
         <v>100</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>497</v>
@@ -5042,7 +5181,7 @@
         <v>100</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>138</v>
@@ -5083,7 +5222,7 @@
         <v>100</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>138</v>
@@ -5124,7 +5263,7 @@
         <v>100</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>138</v>
@@ -5165,7 +5304,7 @@
         <v>100</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>138</v>
@@ -5206,7 +5345,7 @@
         <v>100</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>138</v>
@@ -5247,7 +5386,7 @@
         <v>100</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>140</v>
@@ -5288,7 +5427,7 @@
         <v>100</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>140</v>
@@ -5329,7 +5468,7 @@
         <v>100</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>140</v>
@@ -5370,7 +5509,7 @@
         <v>100</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>140</v>
@@ -5411,7 +5550,7 @@
         <v>100</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>140</v>
@@ -5452,7 +5591,7 @@
         <v>100</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>141</v>
@@ -5493,7 +5632,7 @@
         <v>100</v>
       </c>
       <c r="H49" s="18" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>141</v>
@@ -5534,7 +5673,7 @@
         <v>100</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>141</v>
@@ -5575,7 +5714,7 @@
         <v>100</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>141</v>
@@ -5616,7 +5755,7 @@
         <v>100</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>141</v>
@@ -5657,7 +5796,7 @@
         <v>100</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>143</v>
@@ -5698,7 +5837,7 @@
         <v>100</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>143</v>
@@ -5739,7 +5878,7 @@
         <v>100</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>143</v>
@@ -5780,7 +5919,7 @@
         <v>100</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>143</v>
@@ -5821,7 +5960,7 @@
         <v>100</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>143</v>
@@ -5862,7 +6001,7 @@
         <v>100</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>144</v>
@@ -5903,7 +6042,7 @@
         <v>100</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>144</v>
@@ -5944,7 +6083,7 @@
         <v>100</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>144</v>
@@ -5985,7 +6124,7 @@
         <v>100</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>144</v>
@@ -6026,7 +6165,7 @@
         <v>100</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>144</v>
@@ -6067,7 +6206,7 @@
         <v>100</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>145</v>
@@ -6108,7 +6247,7 @@
         <v>100</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>145</v>
@@ -6149,7 +6288,7 @@
         <v>100</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>145</v>
@@ -6190,7 +6329,7 @@
         <v>100</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>145</v>
@@ -6231,7 +6370,7 @@
         <v>100</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>145</v>
@@ -6272,7 +6411,7 @@
         <v>100</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>147</v>
@@ -6313,7 +6452,7 @@
         <v>100</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>147</v>
@@ -6354,7 +6493,7 @@
         <v>100</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>147</v>
@@ -6395,7 +6534,7 @@
         <v>100</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>147</v>
@@ -6436,7 +6575,7 @@
         <v>100</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>147</v>
@@ -6477,7 +6616,7 @@
         <v>100</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>81</v>
@@ -6518,7 +6657,7 @@
         <v>100</v>
       </c>
       <c r="H74" s="18" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>81</v>
@@ -6559,7 +6698,7 @@
         <v>100</v>
       </c>
       <c r="H75" s="18" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>81</v>
@@ -6600,7 +6739,7 @@
         <v>100</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>81</v>
@@ -6641,7 +6780,7 @@
         <v>100</v>
       </c>
       <c r="H77" s="18" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>81</v>
@@ -6682,7 +6821,7 @@
         <v>100</v>
       </c>
       <c r="H78" s="18" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>82</v>
@@ -6723,7 +6862,7 @@
         <v>100</v>
       </c>
       <c r="H79" s="18" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>82</v>
@@ -6764,7 +6903,7 @@
         <v>100</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>82</v>
@@ -6805,7 +6944,7 @@
         <v>100</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>82</v>
@@ -6846,7 +6985,7 @@
         <v>100</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>82</v>
@@ -6887,7 +7026,7 @@
         <v>100</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>148</v>
@@ -6928,7 +7067,7 @@
         <v>100</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>148</v>
@@ -6969,7 +7108,7 @@
         <v>100</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="I85" s="15" t="s">
         <v>148</v>
@@ -7010,7 +7149,7 @@
         <v>100</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="I86" s="15" t="s">
         <v>148</v>
@@ -7051,7 +7190,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="I87" s="15" t="s">
         <v>148</v>
@@ -7092,7 +7231,7 @@
         <v>100</v>
       </c>
       <c r="H88" s="18" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="I88" s="15" t="s">
         <v>87</v>
@@ -7133,7 +7272,7 @@
         <v>100</v>
       </c>
       <c r="H89" s="18" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="I89" s="15" t="s">
         <v>87</v>
@@ -7174,7 +7313,7 @@
         <v>100</v>
       </c>
       <c r="H90" s="18" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="I90" s="15" t="s">
         <v>87</v>
@@ -7215,7 +7354,7 @@
         <v>100</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="I91" s="15" t="s">
         <v>87</v>
@@ -7256,7 +7395,7 @@
         <v>100</v>
       </c>
       <c r="H92" s="18" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="I92" s="15" t="s">
         <v>87</v>
@@ -7297,7 +7436,7 @@
         <v>100</v>
       </c>
       <c r="H93" s="18" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="I93" s="15" t="s">
         <v>88</v>
@@ -7338,7 +7477,7 @@
         <v>100</v>
       </c>
       <c r="H94" s="18" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="I94" s="15" t="s">
         <v>88</v>
@@ -7379,7 +7518,7 @@
         <v>100</v>
       </c>
       <c r="H95" s="18" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="I95" s="15" t="s">
         <v>88</v>
@@ -7420,7 +7559,7 @@
         <v>100</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="I96" s="15" t="s">
         <v>88</v>
@@ -7461,7 +7600,7 @@
         <v>100</v>
       </c>
       <c r="H97" s="18" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="I97" s="15" t="s">
         <v>88</v>
@@ -7502,7 +7641,7 @@
         <v>100</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="I98" s="15" t="s">
         <v>149</v>
@@ -7543,7 +7682,7 @@
         <v>100</v>
       </c>
       <c r="H99" s="18" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="I99" s="15" t="s">
         <v>149</v>
@@ -7584,7 +7723,7 @@
         <v>100</v>
       </c>
       <c r="H100" s="18" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="I100" s="15" t="s">
         <v>149</v>
@@ -7625,7 +7764,7 @@
         <v>100</v>
       </c>
       <c r="H101" s="18" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="I101" s="15" t="s">
         <v>149</v>
@@ -7666,7 +7805,7 @@
         <v>100</v>
       </c>
       <c r="H102" s="18" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="I102" s="15" t="s">
         <v>149</v>
@@ -7707,7 +7846,7 @@
         <v>100</v>
       </c>
       <c r="H103" s="18" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="I103" s="15" t="s">
         <v>93</v>
@@ -7748,7 +7887,7 @@
         <v>100</v>
       </c>
       <c r="H104" s="18" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="I104" s="15" t="s">
         <v>93</v>
@@ -7789,7 +7928,7 @@
         <v>100</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="I105" s="15" t="s">
         <v>93</v>
@@ -7830,7 +7969,7 @@
         <v>100</v>
       </c>
       <c r="H106" s="18" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="I106" s="15" t="s">
         <v>93</v>
@@ -7871,7 +8010,7 @@
         <v>100</v>
       </c>
       <c r="H107" s="18" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="I107" s="15" t="s">
         <v>93</v>
@@ -7912,7 +8051,7 @@
         <v>100</v>
       </c>
       <c r="H108" s="18" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="I108" s="15" t="s">
         <v>94</v>
@@ -7953,7 +8092,7 @@
         <v>100</v>
       </c>
       <c r="H109" s="18" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="I109" s="15" t="s">
         <v>94</v>
@@ -7994,7 +8133,7 @@
         <v>100</v>
       </c>
       <c r="H110" s="18" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="I110" s="15" t="s">
         <v>94</v>
@@ -8035,7 +8174,7 @@
         <v>100</v>
       </c>
       <c r="H111" s="18" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="I111" s="15" t="s">
         <v>94</v>
@@ -8076,7 +8215,7 @@
         <v>100</v>
       </c>
       <c r="H112" s="18" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="I112" s="15" t="s">
         <v>94</v>
@@ -8117,16 +8256,16 @@
         <v>500</v>
       </c>
       <c r="H113" s="20" t="s">
-        <v>682</v>
+        <v>779</v>
       </c>
       <c r="I113" s="20" t="s">
-        <v>392</v>
+        <v>132</v>
       </c>
       <c r="J113" s="20" t="s">
-        <v>531</v>
+        <v>29</v>
       </c>
       <c r="K113" s="20">
-        <v>3050001</v>
+        <v>3040102</v>
       </c>
       <c r="L113" s="20" t="s">
         <v>503</v>
@@ -8158,16 +8297,16 @@
         <v>500</v>
       </c>
       <c r="H114" s="20" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="I114" s="20" t="s">
-        <v>393</v>
+        <v>132</v>
       </c>
       <c r="J114" s="20" t="s">
-        <v>582</v>
+        <v>29</v>
       </c>
       <c r="K114" s="20">
-        <v>3050301</v>
+        <v>3040102</v>
       </c>
       <c r="L114" s="20" t="s">
         <v>503</v>
@@ -8199,15 +8338,17 @@
         <v>500</v>
       </c>
       <c r="H115" s="20" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="I115" s="20" t="s">
-        <v>532</v>
+        <v>132</v>
       </c>
       <c r="J115" s="20" t="s">
-        <v>588</v>
-      </c>
-      <c r="K115" s="20"/>
+        <v>29</v>
+      </c>
+      <c r="K115" s="20">
+        <v>3040102</v>
+      </c>
       <c r="L115" s="20" t="s">
         <v>503</v>
       </c>
@@ -8238,16 +8379,16 @@
         <v>500</v>
       </c>
       <c r="H116" s="20" t="s">
-        <v>765</v>
+        <v>782</v>
       </c>
       <c r="I116" s="20" t="s">
-        <v>395</v>
+        <v>132</v>
       </c>
       <c r="J116" s="20" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="K116" s="20">
-        <v>3050301</v>
+        <v>3040102</v>
       </c>
       <c r="L116" s="20" t="s">
         <v>503</v>
@@ -8279,16 +8420,16 @@
         <v>500</v>
       </c>
       <c r="H117" s="20" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="I117" s="20" t="s">
-        <v>396</v>
+        <v>132</v>
       </c>
       <c r="J117" s="20" t="s">
-        <v>583</v>
+        <v>29</v>
       </c>
       <c r="K117" s="20">
-        <v>3550501</v>
+        <v>3040102</v>
       </c>
       <c r="L117" s="20" t="s">
         <v>503</v>
@@ -8320,16 +8461,16 @@
         <v>500</v>
       </c>
       <c r="H118" s="20" t="s">
-        <v>766</v>
+        <v>784</v>
       </c>
       <c r="I118" s="20" t="s">
-        <v>397</v>
+        <v>132</v>
       </c>
       <c r="J118" s="20" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="K118" s="20">
-        <v>3050301</v>
+        <v>3040102</v>
       </c>
       <c r="L118" s="20" t="s">
         <v>503</v>
@@ -8361,15 +8502,17 @@
         <v>500</v>
       </c>
       <c r="H119" s="20" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="I119" s="20" t="s">
-        <v>398</v>
+        <v>132</v>
       </c>
       <c r="J119" s="20" t="s">
-        <v>791</v>
-      </c>
-      <c r="K119" s="20"/>
+        <v>29</v>
+      </c>
+      <c r="K119" s="20">
+        <v>3040102</v>
+      </c>
       <c r="L119" s="20" t="s">
         <v>503</v>
       </c>
@@ -8400,16 +8543,16 @@
         <v>500</v>
       </c>
       <c r="H120" s="20" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="I120" s="20" t="s">
-        <v>399</v>
+        <v>132</v>
       </c>
       <c r="J120" s="20" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="K120" s="20">
-        <v>3050301</v>
+        <v>3040102</v>
       </c>
       <c r="L120" s="20" t="s">
         <v>503</v>
@@ -8441,13 +8584,13 @@
         <v>500</v>
       </c>
       <c r="H121" s="22" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="I121" s="22" t="s">
         <v>405</v>
       </c>
       <c r="J121" s="22" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K121" s="22">
         <v>3060001</v>
@@ -8482,13 +8625,13 @@
         <v>500</v>
       </c>
       <c r="H122" s="22" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="I122" s="22" t="s">
         <v>403</v>
       </c>
       <c r="J122" s="22" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="K122" s="22">
         <v>3060102</v>
@@ -8523,13 +8666,13 @@
         <v>500</v>
       </c>
       <c r="H123" s="22" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="I123" s="22" t="s">
         <v>416</v>
       </c>
       <c r="J123" s="22" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="K123" s="22"/>
       <c r="L123" s="22" t="s">
@@ -8562,13 +8705,13 @@
         <v>500</v>
       </c>
       <c r="H124" s="22" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="I124" s="22" t="s">
         <v>404</v>
       </c>
       <c r="J124" s="22" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="K124" s="24" t="s">
         <v>476</v>
@@ -8603,13 +8746,13 @@
         <v>500</v>
       </c>
       <c r="H125" s="22" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="I125" s="22" t="s">
         <v>400</v>
       </c>
       <c r="J125" s="22" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="K125" s="22"/>
       <c r="L125" s="22" t="s">
@@ -8642,13 +8785,13 @@
         <v>500</v>
       </c>
       <c r="H126" s="22" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="I126" s="22" t="s">
         <v>406</v>
       </c>
       <c r="J126" s="22" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K126" s="22">
         <v>3060102</v>
@@ -8683,13 +8826,13 @@
         <v>500</v>
       </c>
       <c r="H127" s="22" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="I127" s="22" t="s">
         <v>401</v>
       </c>
       <c r="J127" s="22" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K127" s="22">
         <v>3060102</v>
@@ -8724,7 +8867,7 @@
         <v>500</v>
       </c>
       <c r="H128" s="22" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="I128" s="22" t="s">
         <v>407</v>
@@ -8763,7 +8906,7 @@
         <v>500</v>
       </c>
       <c r="H129" s="26" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="I129" s="26" t="s">
         <v>402</v>
@@ -8804,7 +8947,7 @@
         <v>500</v>
       </c>
       <c r="H130" s="26" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="I130" s="26" t="s">
         <v>408</v>
@@ -8845,7 +8988,7 @@
         <v>500</v>
       </c>
       <c r="H131" s="26" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="I131" s="26" t="s">
         <v>411</v>
@@ -8884,7 +9027,7 @@
         <v>500</v>
       </c>
       <c r="H132" s="26" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="I132" s="26" t="s">
         <v>409</v>
@@ -8925,7 +9068,7 @@
         <v>500</v>
       </c>
       <c r="H133" s="26" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="I133" s="26" t="s">
         <v>410</v>
@@ -8964,7 +9107,7 @@
         <v>500</v>
       </c>
       <c r="H134" s="26" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="I134" s="26" t="s">
         <v>504</v>
@@ -9005,7 +9148,7 @@
         <v>500</v>
       </c>
       <c r="H135" s="26" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="I135" s="26" t="s">
         <v>412</v>
@@ -9046,7 +9189,7 @@
         <v>500</v>
       </c>
       <c r="H136" s="26" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="I136" s="26" t="s">
         <v>413</v>
@@ -9085,7 +9228,7 @@
         <v>500</v>
       </c>
       <c r="H137" s="30" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="I137" s="30" t="s">
         <v>414</v>
@@ -9126,7 +9269,7 @@
         <v>500</v>
       </c>
       <c r="H138" s="30" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="I138" s="30" t="s">
         <v>415</v>
@@ -9167,7 +9310,7 @@
         <v>500</v>
       </c>
       <c r="H139" s="30" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="I139" s="30" t="s">
         <v>419</v>
@@ -9208,7 +9351,7 @@
         <v>500</v>
       </c>
       <c r="H140" s="30" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="I140" s="30" t="s">
         <v>417</v>
@@ -9249,7 +9392,7 @@
         <v>500</v>
       </c>
       <c r="H141" s="30" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="I141" s="30" t="s">
         <v>420</v>
@@ -9290,7 +9433,7 @@
         <v>500</v>
       </c>
       <c r="H142" s="30" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="I142" s="30" t="s">
         <v>421</v>
@@ -9331,7 +9474,7 @@
         <v>500</v>
       </c>
       <c r="H143" s="30" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="I143" s="30" t="s">
         <v>422</v>
@@ -9372,7 +9515,7 @@
         <v>500</v>
       </c>
       <c r="H144" s="30" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="I144" s="30" t="s">
         <v>418</v>
@@ -9413,7 +9556,7 @@
         <v>500</v>
       </c>
       <c r="H145" s="36" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="I145" s="34" t="s">
         <v>440</v>
@@ -9454,7 +9597,7 @@
         <v>500</v>
       </c>
       <c r="H146" s="36" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="I146" s="34" t="s">
         <v>424</v>
@@ -9495,7 +9638,7 @@
         <v>500</v>
       </c>
       <c r="H147" s="36" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="I147" s="34" t="s">
         <v>425</v>
@@ -9536,7 +9679,7 @@
         <v>500</v>
       </c>
       <c r="H148" s="36" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="I148" s="34" t="s">
         <v>423</v>
@@ -9575,7 +9718,7 @@
         <v>500</v>
       </c>
       <c r="H149" s="36" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="I149" s="34" t="s">
         <v>445</v>
@@ -9616,7 +9759,7 @@
         <v>500</v>
       </c>
       <c r="H150" s="36" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="I150" s="34" t="s">
         <v>426</v>
@@ -9655,7 +9798,7 @@
         <v>500</v>
       </c>
       <c r="H151" s="39" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="I151" s="37" t="s">
         <v>447</v>
@@ -9696,16 +9839,16 @@
         <v>500</v>
       </c>
       <c r="H152" s="39" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="I152" s="37" t="s">
         <v>448</v>
       </c>
       <c r="J152" s="37" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="K152" s="39" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="L152" s="37" t="s">
         <v>502</v>
@@ -9737,16 +9880,16 @@
         <v>500</v>
       </c>
       <c r="H153" s="39" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="I153" s="37" t="s">
         <v>449</v>
       </c>
       <c r="J153" s="37" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="K153" s="39" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="L153" s="37" t="s">
         <v>503</v>
@@ -9778,13 +9921,13 @@
         <v>500</v>
       </c>
       <c r="H154" s="39" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="I154" s="37" t="s">
         <v>450</v>
       </c>
       <c r="J154" s="37" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="K154" s="37"/>
       <c r="L154" s="37" t="s">
@@ -9817,13 +9960,13 @@
         <v>500</v>
       </c>
       <c r="H155" s="39" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="I155" s="37" t="s">
         <v>451</v>
       </c>
       <c r="J155" s="37" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="K155" s="37"/>
       <c r="L155" s="37" t="s">
@@ -9856,16 +9999,16 @@
         <v>500</v>
       </c>
       <c r="H156" s="39" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="I156" s="37" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="J156" s="37" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="K156" s="39" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="L156" s="37" t="s">
         <v>503</v>
@@ -9897,7 +10040,7 @@
         <v>500</v>
       </c>
       <c r="H157" s="39" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="I157" s="37" t="s">
         <v>453</v>
@@ -9936,7 +10079,7 @@
         <v>500</v>
       </c>
       <c r="H158" s="39" t="s">
-        <v>786</v>
+        <v>775</v>
       </c>
       <c r="I158" s="37" t="s">
         <v>455</v>
@@ -9975,7 +10118,7 @@
         <v>500</v>
       </c>
       <c r="H159" s="43" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="I159" s="41" t="s">
         <v>470</v>
@@ -10016,7 +10159,7 @@
         <v>500</v>
       </c>
       <c r="H160" s="43" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="I160" s="41" t="s">
         <v>457</v>
@@ -10055,7 +10198,7 @@
         <v>500</v>
       </c>
       <c r="H161" s="43" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="I161" s="41" t="s">
         <v>459</v>
@@ -10094,7 +10237,7 @@
         <v>500</v>
       </c>
       <c r="H162" s="43" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="I162" s="41" t="s">
         <v>460</v>
@@ -10133,7 +10276,7 @@
         <v>500</v>
       </c>
       <c r="H163" s="43" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="I163" s="41" t="s">
         <v>462</v>
@@ -10172,7 +10315,7 @@
         <v>500</v>
       </c>
       <c r="H164" s="43" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="I164" s="41" t="s">
         <v>463</v>
@@ -10211,7 +10354,7 @@
         <v>500</v>
       </c>
       <c r="H165" s="43" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="I165" s="41" t="s">
         <v>465</v>
@@ -10252,7 +10395,7 @@
         <v>500</v>
       </c>
       <c r="H166" s="43" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="I166" s="41" t="s">
         <v>466</v>
@@ -10282,7 +10425,7 @@
         <v>1</v>
       </c>
       <c r="E167" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F167" s="45">
         <v>1</v>
@@ -10291,13 +10434,13 @@
         <v>1</v>
       </c>
       <c r="H167" s="45" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="I167" s="45" t="s">
         <v>506</v>
       </c>
       <c r="J167" s="45" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K167" s="45"/>
       <c r="L167" s="45" t="s">
@@ -10321,7 +10464,7 @@
         <v>1</v>
       </c>
       <c r="E168" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F168" s="45">
         <v>1</v>
@@ -10330,13 +10473,13 @@
         <v>1</v>
       </c>
       <c r="H168" s="45" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="I168" s="45" t="s">
         <v>507</v>
       </c>
       <c r="J168" s="45" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K168" s="45"/>
       <c r="L168" s="45" t="s">
@@ -10360,7 +10503,7 @@
         <v>1</v>
       </c>
       <c r="E169" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F169" s="45">
         <v>1</v>
@@ -10369,13 +10512,13 @@
         <v>1</v>
       </c>
       <c r="H169" s="45" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="I169" s="45" t="s">
         <v>508</v>
       </c>
       <c r="J169" s="45" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K169" s="45"/>
       <c r="L169" s="45" t="s">
@@ -10399,7 +10542,7 @@
         <v>1</v>
       </c>
       <c r="E170" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F170" s="45">
         <v>1</v>
@@ -10408,13 +10551,13 @@
         <v>1</v>
       </c>
       <c r="H170" s="45" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="I170" s="45" t="s">
         <v>509</v>
       </c>
       <c r="J170" s="45" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K170" s="45"/>
       <c r="L170" s="45" t="s">
@@ -10438,7 +10581,7 @@
         <v>1</v>
       </c>
       <c r="E171" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F171" s="45">
         <v>1</v>
@@ -10447,13 +10590,13 @@
         <v>1</v>
       </c>
       <c r="H171" s="45" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="I171" s="45" t="s">
         <v>510</v>
       </c>
       <c r="J171" s="45" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K171" s="45"/>
       <c r="L171" s="45" t="s">
@@ -10477,7 +10620,7 @@
         <v>1</v>
       </c>
       <c r="E172" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F172" s="45">
         <v>1</v>
@@ -10486,13 +10629,13 @@
         <v>1</v>
       </c>
       <c r="H172" s="45" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="I172" s="45" t="s">
         <v>511</v>
       </c>
       <c r="J172" s="45" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K172" s="45"/>
       <c r="L172" s="45" t="s">
@@ -10516,7 +10659,7 @@
         <v>1</v>
       </c>
       <c r="E173" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F173" s="45">
         <v>1</v>
@@ -10525,13 +10668,13 @@
         <v>1</v>
       </c>
       <c r="H173" s="45" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="I173" s="45" t="s">
         <v>512</v>
       </c>
       <c r="J173" s="45" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K173" s="45"/>
       <c r="L173" s="45" t="s">
@@ -10555,7 +10698,7 @@
         <v>1</v>
       </c>
       <c r="E174" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F174" s="45">
         <v>1</v>
@@ -10564,13 +10707,13 @@
         <v>1</v>
       </c>
       <c r="H174" s="45" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="I174" s="45" t="s">
         <v>513</v>
       </c>
       <c r="J174" s="45" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K174" s="45"/>
       <c r="L174" s="45" t="s">
@@ -10594,7 +10737,7 @@
         <v>1</v>
       </c>
       <c r="E175" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F175" s="45">
         <v>1</v>
@@ -10603,13 +10746,13 @@
         <v>1</v>
       </c>
       <c r="H175" s="45" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="I175" s="45" t="s">
         <v>514</v>
       </c>
       <c r="J175" s="45" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K175" s="45"/>
       <c r="L175" s="45" t="s">
@@ -10633,7 +10776,7 @@
         <v>1</v>
       </c>
       <c r="E176" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F176" s="45">
         <v>1</v>
@@ -10642,13 +10785,13 @@
         <v>1</v>
       </c>
       <c r="H176" s="45" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="I176" s="45" t="s">
         <v>515</v>
       </c>
       <c r="J176" s="45" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K176" s="45"/>
       <c r="L176" s="45" t="s">
@@ -10672,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="E177" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F177" s="45">
         <v>1</v>
@@ -10681,13 +10824,13 @@
         <v>1</v>
       </c>
       <c r="H177" s="45" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="I177" s="45" t="s">
         <v>516</v>
       </c>
       <c r="J177" s="45" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K177" s="45"/>
       <c r="L177" s="45" t="s">
@@ -10711,7 +10854,7 @@
         <v>1</v>
       </c>
       <c r="E178" s="46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F178" s="45">
         <v>1</v>
@@ -10720,13 +10863,13 @@
         <v>1</v>
       </c>
       <c r="H178" s="45" t="s">
-        <v>729</v>
+        <v>786</v>
       </c>
       <c r="I178" s="45" t="s">
-        <v>517</v>
+        <v>787</v>
       </c>
       <c r="J178" s="45" t="s">
-        <v>529</v>
+        <v>788</v>
       </c>
       <c r="K178" s="45"/>
       <c r="L178" s="45" t="s">
@@ -10750,7 +10893,7 @@
         <v>1</v>
       </c>
       <c r="E179" s="21" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F179" s="20">
         <v>1</v>
@@ -10759,13 +10902,13 @@
         <v>500</v>
       </c>
       <c r="H179" s="20" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="I179" s="20" t="s">
         <v>392</v>
       </c>
       <c r="J179" s="48" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="K179" s="20">
         <v>3050001</v>
@@ -10800,13 +10943,13 @@
         <v>500</v>
       </c>
       <c r="H180" s="20" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="I180" s="20" t="s">
         <v>393</v>
       </c>
       <c r="J180" s="48" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="K180" s="20">
         <v>3050301</v>
@@ -10841,13 +10984,13 @@
         <v>500</v>
       </c>
       <c r="H181" s="20" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="I181" s="20" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J181" s="48" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="K181" s="20"/>
       <c r="L181" s="20" t="s">
@@ -10880,13 +11023,13 @@
         <v>500</v>
       </c>
       <c r="H182" s="20" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="I182" s="20" t="s">
         <v>395</v>
       </c>
       <c r="J182" s="48" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="K182" s="20">
         <v>3050301</v>
@@ -10921,13 +11064,13 @@
         <v>500</v>
       </c>
       <c r="H183" s="20" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="I183" s="20" t="s">
         <v>396</v>
       </c>
       <c r="J183" s="48" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="K183" s="20">
         <v>3550501</v>
@@ -10962,13 +11105,13 @@
         <v>500</v>
       </c>
       <c r="H184" s="20" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="I184" s="20" t="s">
         <v>397</v>
       </c>
       <c r="J184" s="48" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="K184" s="20">
         <v>3550206</v>
@@ -11003,13 +11146,13 @@
         <v>500</v>
       </c>
       <c r="H185" s="20" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="I185" s="20" t="s">
         <v>398</v>
       </c>
       <c r="J185" s="48" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="K185" s="20">
         <v>3050301</v>
@@ -11044,16 +11187,16 @@
         <v>500</v>
       </c>
       <c r="H186" s="20" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="I186" s="20" t="s">
         <v>399</v>
       </c>
       <c r="J186" s="48" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K186" s="49" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="L186" s="20" t="s">
         <v>502</v>
@@ -11085,10 +11228,10 @@
         <v>500</v>
       </c>
       <c r="H187" s="20" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="I187" s="20" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J187" s="48" t="s">
         <v>48</v>
@@ -11117,7 +11260,7 @@
         <v>1</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F188" s="22">
         <v>1</v>
@@ -11126,13 +11269,13 @@
         <v>500</v>
       </c>
       <c r="H188" s="22" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="I188" s="22" t="s">
         <v>490</v>
       </c>
       <c r="J188" s="22" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K188" s="22">
         <v>3060001</v>
@@ -11167,13 +11310,13 @@
         <v>500</v>
       </c>
       <c r="H189" s="22" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I189" s="22" t="s">
         <v>491</v>
       </c>
       <c r="J189" s="22" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="K189" s="22">
         <v>3060102</v>
@@ -11208,13 +11351,13 @@
         <v>500</v>
       </c>
       <c r="H190" s="22" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I190" s="22" t="s">
         <v>492</v>
       </c>
       <c r="J190" s="22" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="K190" s="22"/>
       <c r="L190" s="22" t="s">
@@ -11247,13 +11390,13 @@
         <v>500</v>
       </c>
       <c r="H191" s="22" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="I191" s="22" t="s">
         <v>493</v>
       </c>
       <c r="J191" s="22" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="K191" s="24" t="s">
         <v>476</v>
@@ -11288,13 +11431,13 @@
         <v>500</v>
       </c>
       <c r="H192" s="22" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="I192" s="22" t="s">
         <v>400</v>
       </c>
       <c r="J192" s="22" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="K192" s="22">
         <v>3560501</v>
@@ -11329,13 +11472,13 @@
         <v>500</v>
       </c>
       <c r="H193" s="22" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="I193" s="22" t="s">
         <v>494</v>
       </c>
       <c r="J193" s="22" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K193" s="22">
         <v>3060102</v>
@@ -11370,13 +11513,13 @@
         <v>500</v>
       </c>
       <c r="H194" s="22" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="I194" s="22" t="s">
         <v>401</v>
       </c>
       <c r="J194" s="22" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K194" s="22">
         <v>3060102</v>
@@ -11411,7 +11554,7 @@
         <v>500</v>
       </c>
       <c r="H195" s="22" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="I195" s="22" t="s">
         <v>495</v>
@@ -11441,7 +11584,7 @@
         <v>1</v>
       </c>
       <c r="E196" s="27" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F196" s="26">
         <v>1</v>
@@ -11450,13 +11593,13 @@
         <v>500</v>
       </c>
       <c r="H196" s="26" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="I196" s="26" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="J196" s="26" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K196" s="26">
         <v>3070001</v>
@@ -11491,13 +11634,13 @@
         <v>500</v>
       </c>
       <c r="H197" s="26" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="I197" s="26" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J197" s="26" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="K197" s="28" t="s">
         <v>477</v>
@@ -11532,13 +11675,13 @@
         <v>500</v>
       </c>
       <c r="H198" s="26" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="I198" s="26" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="J198" s="26" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="K198" s="26"/>
       <c r="L198" s="26" t="s">
@@ -11571,13 +11714,13 @@
         <v>500</v>
       </c>
       <c r="H199" s="26" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="I199" s="26" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="J199" s="26" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K199" s="28" t="s">
         <v>477</v>
@@ -11612,13 +11755,13 @@
         <v>500</v>
       </c>
       <c r="H200" s="26" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I200" s="26" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="J200" s="26" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="K200" s="26">
         <v>3570701</v>
@@ -11653,13 +11796,13 @@
         <v>500</v>
       </c>
       <c r="H201" s="26" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="I201" s="26" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J201" s="26" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="K201" s="26">
         <v>3070102</v>
@@ -11694,13 +11837,13 @@
         <v>500</v>
       </c>
       <c r="H202" s="26" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="I202" s="26" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="J202" s="26" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="K202" s="26">
         <v>3070102</v>
@@ -11735,13 +11878,13 @@
         <v>500</v>
       </c>
       <c r="H203" s="26" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="I203" s="26" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J203" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="K203" s="29"/>
       <c r="L203" s="26" t="s">
@@ -11765,7 +11908,7 @@
         <v>1</v>
       </c>
       <c r="E204" s="31" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F204" s="30">
         <v>1</v>
@@ -11774,13 +11917,13 @@
         <v>500</v>
       </c>
       <c r="H204" s="30" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="I204" s="30" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="J204" s="30" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="K204" s="30">
         <v>3080001</v>
@@ -11815,13 +11958,13 @@
         <v>500</v>
       </c>
       <c r="H205" s="30" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="I205" s="30" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="J205" s="30" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="K205" s="32" t="s">
         <v>467</v>
@@ -11856,13 +11999,13 @@
         <v>500</v>
       </c>
       <c r="H206" s="30" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="I206" s="30" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J206" s="30" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="K206" s="30">
         <v>3080102</v>
@@ -11897,13 +12040,13 @@
         <v>500</v>
       </c>
       <c r="H207" s="30" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="I207" s="30" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="J207" s="30" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="K207" s="30">
         <v>3080102</v>
@@ -11938,13 +12081,13 @@
         <v>500</v>
       </c>
       <c r="H208" s="30" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="I208" s="30" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J208" s="30" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="K208" s="30">
         <v>3080102</v>
@@ -11979,13 +12122,13 @@
         <v>500</v>
       </c>
       <c r="H209" s="30" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="I209" s="30" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J209" s="30" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="K209" s="30">
         <v>3080102</v>
@@ -12020,13 +12163,13 @@
         <v>500</v>
       </c>
       <c r="H210" s="30" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="I210" s="30" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J210" s="30" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="K210" s="30">
         <v>3080102</v>
@@ -12061,13 +12204,13 @@
         <v>500</v>
       </c>
       <c r="H211" s="30" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="I211" s="30" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="J211" s="30" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="K211" s="33" t="s">
         <v>468</v>
@@ -12077,6 +12220,729 @@
       </c>
       <c r="M211" s="32">
         <v>3580001</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+      <c r="A212" s="15">
+        <v>99990001</v>
+      </c>
+      <c r="B212" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C212" s="15">
+        <v>1</v>
+      </c>
+      <c r="D212" s="15">
+        <v>1</v>
+      </c>
+      <c r="E212" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F212" s="15">
+        <v>1</v>
+      </c>
+      <c r="G212" s="15">
+        <v>100</v>
+      </c>
+      <c r="H212" s="18" t="s">
+        <v>802</v>
+      </c>
+      <c r="I212" s="15" t="s">
+        <v>789</v>
+      </c>
+      <c r="J212" s="15" t="s">
+        <v>789</v>
+      </c>
+      <c r="K212" s="15"/>
+      <c r="L212" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M212" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+      <c r="A213" s="15">
+        <v>99990002</v>
+      </c>
+      <c r="B213" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C213" s="15">
+        <v>2</v>
+      </c>
+      <c r="D213" s="15">
+        <v>1</v>
+      </c>
+      <c r="E213" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F213" s="15">
+        <v>1</v>
+      </c>
+      <c r="G213" s="15">
+        <v>100</v>
+      </c>
+      <c r="H213" s="18" t="s">
+        <v>803</v>
+      </c>
+      <c r="I213" s="16" t="s">
+        <v>790</v>
+      </c>
+      <c r="J213" s="16" t="s">
+        <v>790</v>
+      </c>
+      <c r="L213" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M213" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+      <c r="A214" s="15">
+        <v>99990003</v>
+      </c>
+      <c r="B214" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C214" s="15">
+        <v>3</v>
+      </c>
+      <c r="D214" s="15">
+        <v>1</v>
+      </c>
+      <c r="E214" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F214" s="15">
+        <v>1</v>
+      </c>
+      <c r="G214" s="15">
+        <v>100</v>
+      </c>
+      <c r="H214" s="18" t="s">
+        <v>804</v>
+      </c>
+      <c r="I214" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="J214" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="L214" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M214" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A215" s="15">
+        <v>99990004</v>
+      </c>
+      <c r="B215" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C215" s="15">
+        <v>4</v>
+      </c>
+      <c r="D215" s="15">
+        <v>1</v>
+      </c>
+      <c r="E215" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F215" s="15">
+        <v>1</v>
+      </c>
+      <c r="G215" s="15">
+        <v>100</v>
+      </c>
+      <c r="H215" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="I215" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="J215" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="L215" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M215" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A216" s="15">
+        <v>99990005</v>
+      </c>
+      <c r="B216" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C216" s="15">
+        <v>5</v>
+      </c>
+      <c r="D216" s="15">
+        <v>1</v>
+      </c>
+      <c r="E216" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F216" s="15">
+        <v>1</v>
+      </c>
+      <c r="G216" s="15">
+        <v>100</v>
+      </c>
+      <c r="H216" s="16" t="s">
+        <v>806</v>
+      </c>
+      <c r="I216" s="16" t="s">
+        <v>793</v>
+      </c>
+      <c r="J216" s="16" t="s">
+        <v>793</v>
+      </c>
+      <c r="L216" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M216" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A217" s="15">
+        <v>99990006</v>
+      </c>
+      <c r="B217" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C217" s="15">
+        <v>6</v>
+      </c>
+      <c r="D217" s="15">
+        <v>1</v>
+      </c>
+      <c r="E217" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F217" s="15">
+        <v>1</v>
+      </c>
+      <c r="G217" s="15">
+        <v>100</v>
+      </c>
+      <c r="H217" s="16" t="s">
+        <v>807</v>
+      </c>
+      <c r="I217" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="J217" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="L217" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M217" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A218" s="15">
+        <v>99990007</v>
+      </c>
+      <c r="B218" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C218" s="15">
+        <v>7</v>
+      </c>
+      <c r="D218" s="15">
+        <v>1</v>
+      </c>
+      <c r="E218" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F218" s="15">
+        <v>1</v>
+      </c>
+      <c r="G218" s="15">
+        <v>100</v>
+      </c>
+      <c r="H218" s="16" t="s">
+        <v>808</v>
+      </c>
+      <c r="I218" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="J218" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="L218" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M218" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A219" s="15">
+        <v>99990008</v>
+      </c>
+      <c r="B219" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C219" s="15">
+        <v>8</v>
+      </c>
+      <c r="D219" s="15">
+        <v>1</v>
+      </c>
+      <c r="E219" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F219" s="15">
+        <v>1</v>
+      </c>
+      <c r="G219" s="15">
+        <v>100</v>
+      </c>
+      <c r="H219" s="16" t="s">
+        <v>809</v>
+      </c>
+      <c r="I219" s="16" t="s">
+        <v>796</v>
+      </c>
+      <c r="J219" s="16" t="s">
+        <v>796</v>
+      </c>
+      <c r="L219" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M219" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A220" s="15">
+        <v>99990009</v>
+      </c>
+      <c r="B220" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C220" s="15">
+        <v>9</v>
+      </c>
+      <c r="D220" s="15">
+        <v>1</v>
+      </c>
+      <c r="E220" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F220" s="15">
+        <v>1</v>
+      </c>
+      <c r="G220" s="15">
+        <v>100</v>
+      </c>
+      <c r="H220" s="16" t="s">
+        <v>810</v>
+      </c>
+      <c r="I220" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="J220" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="L220" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M220" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A221" s="15">
+        <v>99990010</v>
+      </c>
+      <c r="B221" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C221" s="15">
+        <v>10</v>
+      </c>
+      <c r="D221" s="15">
+        <v>1</v>
+      </c>
+      <c r="E221" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F221" s="15">
+        <v>1</v>
+      </c>
+      <c r="G221" s="15">
+        <v>100</v>
+      </c>
+      <c r="H221" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="I221" s="16" t="s">
+        <v>798</v>
+      </c>
+      <c r="J221" s="16" t="s">
+        <v>798</v>
+      </c>
+      <c r="L221" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M221" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A222" s="15">
+        <v>99990011</v>
+      </c>
+      <c r="B222" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C222" s="15">
+        <v>11</v>
+      </c>
+      <c r="D222" s="15">
+        <v>1</v>
+      </c>
+      <c r="E222" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F222" s="15">
+        <v>1</v>
+      </c>
+      <c r="G222" s="15">
+        <v>100</v>
+      </c>
+      <c r="H222" s="16" t="s">
+        <v>812</v>
+      </c>
+      <c r="I222" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="J222" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="L222" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M222" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A223" s="15">
+        <v>99990012</v>
+      </c>
+      <c r="B223" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C223" s="15">
+        <v>12</v>
+      </c>
+      <c r="D223" s="15">
+        <v>1</v>
+      </c>
+      <c r="E223" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F223" s="15">
+        <v>1</v>
+      </c>
+      <c r="G223" s="15">
+        <v>100</v>
+      </c>
+      <c r="H223" s="16" t="s">
+        <v>813</v>
+      </c>
+      <c r="I223" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="J223" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="L223" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M223" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A224" s="15">
+        <v>99990013</v>
+      </c>
+      <c r="B224" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C224" s="15">
+        <v>13</v>
+      </c>
+      <c r="D224" s="15">
+        <v>1</v>
+      </c>
+      <c r="E224" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F224" s="15">
+        <v>1</v>
+      </c>
+      <c r="G224" s="15">
+        <v>100</v>
+      </c>
+      <c r="H224" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="I224" s="16" t="s">
+        <v>816</v>
+      </c>
+      <c r="J224" s="16" t="s">
+        <v>816</v>
+      </c>
+      <c r="L224" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M224" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A225" s="15">
+        <v>99990014</v>
+      </c>
+      <c r="B225" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C225" s="15">
+        <v>14</v>
+      </c>
+      <c r="D225" s="15">
+        <v>1</v>
+      </c>
+      <c r="E225" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F225" s="15">
+        <v>1</v>
+      </c>
+      <c r="G225" s="15">
+        <v>100</v>
+      </c>
+      <c r="H225" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="I225" s="16" t="s">
+        <v>800</v>
+      </c>
+      <c r="J225" s="16" t="s">
+        <v>800</v>
+      </c>
+      <c r="L225" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M225" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A226" s="15">
+        <v>99990015</v>
+      </c>
+      <c r="B226" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C226" s="15">
+        <v>15</v>
+      </c>
+      <c r="D226" s="15">
+        <v>1</v>
+      </c>
+      <c r="E226" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F226" s="15">
+        <v>1</v>
+      </c>
+      <c r="G226" s="15">
+        <v>100</v>
+      </c>
+      <c r="H226" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="I226" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="J226" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="L226" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M226" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A227" s="15">
+        <v>99990016</v>
+      </c>
+      <c r="B227" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C227" s="15">
+        <v>16</v>
+      </c>
+      <c r="D227" s="15">
+        <v>1</v>
+      </c>
+      <c r="E227" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F227" s="15">
+        <v>1</v>
+      </c>
+      <c r="G227" s="15">
+        <v>100</v>
+      </c>
+      <c r="H227" s="16" t="s">
+        <v>821</v>
+      </c>
+      <c r="I227" s="16" t="s">
+        <v>820</v>
+      </c>
+      <c r="J227" s="16" t="s">
+        <v>820</v>
+      </c>
+      <c r="L227" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M227" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A228" s="15">
+        <v>99990017</v>
+      </c>
+      <c r="B228" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C228" s="15">
+        <v>17</v>
+      </c>
+      <c r="D228" s="15">
+        <v>1</v>
+      </c>
+      <c r="E228" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F228" s="15">
+        <v>1</v>
+      </c>
+      <c r="G228" s="15">
+        <v>100</v>
+      </c>
+      <c r="H228" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="I228" s="16" t="s">
+        <v>822</v>
+      </c>
+      <c r="J228" s="16" t="s">
+        <v>822</v>
+      </c>
+      <c r="L228" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M228" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A229" s="15">
+        <v>99990018</v>
+      </c>
+      <c r="B229" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C229" s="15">
+        <v>18</v>
+      </c>
+      <c r="D229" s="15">
+        <v>1</v>
+      </c>
+      <c r="E229" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F229" s="15">
+        <v>1</v>
+      </c>
+      <c r="G229" s="15">
+        <v>100</v>
+      </c>
+      <c r="H229" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="I229" s="16" t="s">
+        <v>824</v>
+      </c>
+      <c r="J229" s="16" t="s">
+        <v>824</v>
+      </c>
+      <c r="L229" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M229" s="15">
+        <v>3600002</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A230" s="15">
+        <v>99990019</v>
+      </c>
+      <c r="B230" s="15">
+        <v>9999</v>
+      </c>
+      <c r="C230" s="15">
+        <v>19</v>
+      </c>
+      <c r="D230" s="15">
+        <v>1</v>
+      </c>
+      <c r="E230" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F230" s="15">
+        <v>1</v>
+      </c>
+      <c r="G230" s="15">
+        <v>100</v>
+      </c>
+      <c r="H230" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="I230" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="J230" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="L230" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="M230" s="15">
+        <v>3600002</v>
       </c>
     </row>
   </sheetData>
